--- a/Q1_Q2_Q3_SQL_Analysis/Q2_loan_portfolio_risk/Q2_loan_portfolio_risk.xlsx
+++ b/Q1_Q2_Q3_SQL_Analysis/Q2_loan_portfolio_risk/Q2_loan_portfolio_risk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mine\Dialog\dialog-finance-analytics\Q1_Q2_Q3_SQL_Analysis\Q2_loan_portfolio_risk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E89AD99F-EA65-4DA5-B278-CC70DABC8FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827E3027-6869-4EE0-948D-E3F915EA1449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -848,7 +848,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="\L\K\R\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="\L\K\R\ #,##0.00"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -882,6 +882,7 @@
     </font>
     <font>
       <b/>
+      <u/>
       <sz val="18"/>
       <color theme="1"/>
       <name val="Consolas"/>
@@ -889,6 +890,7 @@
     </font>
     <font>
       <b/>
+      <u/>
       <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -928,7 +930,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -940,7 +942,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -955,39 +957,6 @@
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="61">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1121,6 +1090,24 @@
       <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1138,6 +1125,21 @@
     <dxf>
       <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{84C151FA-0B47-4594-87AA-EE11854CB5E4}"/>
@@ -1154,124 +1156,124 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{12C6653D-EEDA-404A-9B3E-2019BAD080D8}" name="Table2" displayName="Table2" ref="B7:D8" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{12C6653D-EEDA-404A-9B3E-2019BAD080D8}" name="Table2" displayName="Table2" ref="B7:D8" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59">
   <autoFilter ref="B7:D8" xr:uid="{12C6653D-EEDA-404A-9B3E-2019BAD080D8}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{199BCFEF-1354-48F2-BE89-878A8B1BC970}" name="total_customers" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{6C6BA2B9-59F7-4F8E-B70F-847640F7FF1E}" name="customers_with_loan" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{BBD27FC1-F567-4DAC-BAE9-BCDE7B87881A}" name="penetration_rate_pct" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{199BCFEF-1354-48F2-BE89-878A8B1BC970}" name="total_customers" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{6C6BA2B9-59F7-4F8E-B70F-847640F7FF1E}" name="customers_with_loan" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{BBD27FC1-F567-4DAC-BAE9-BCDE7B87881A}" name="penetration_rate_pct" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03810415-CF29-4566-B4E3-EFB98E081303}" name="Table3" displayName="Table3" ref="B14:E18" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59">
-  <autoFilter ref="B14:E18" xr:uid="{03810415-CF29-4566-B4E3-EFB98E081303}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03810415-CF29-4566-B4E3-EFB98E081303}" name="Table3" displayName="Table3" ref="B14:E17" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+  <autoFilter ref="B14:E17" xr:uid="{03810415-CF29-4566-B4E3-EFB98E081303}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{1503ED78-1E64-47B5-9EB0-A4FC7075B396}" name="customer_segment" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{C34C360F-98B9-423A-B753-DF6482A355DD}" name="total_customers" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{111C2081-75BA-4CE6-B34B-ECD55F7A2FFB}" name="customers_with_loan" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{EF53A14F-9001-4BED-B7BF-619A2067BAB7}" name="penetration_rate_pct %" dataDxfId="55"/>
+    <tableColumn id="1" xr3:uid="{1503ED78-1E64-47B5-9EB0-A4FC7075B396}" name="customer_segment" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{C34C360F-98B9-423A-B753-DF6482A355DD}" name="total_customers" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{111C2081-75BA-4CE6-B34B-ECD55F7A2FFB}" name="customers_with_loan" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{EF53A14F-9001-4BED-B7BF-619A2067BAB7}" name="penetration_rate_pct %" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8E873EDB-B72A-4D29-8186-9CFEE6AD1209}" name="Table4" displayName="Table4" ref="B23:E27" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="B23:E27" xr:uid="{8E873EDB-B72A-4D29-8186-9CFEE6AD1209}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8E873EDB-B72A-4D29-8186-9CFEE6AD1209}" name="Table4" displayName="Table4" ref="B22:E26" totalsRowShown="0" headerRowDxfId="49" dataDxfId="48">
+  <autoFilter ref="B22:E26" xr:uid="{8E873EDB-B72A-4D29-8186-9CFEE6AD1209}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{67435B00-5F3D-4084-B4C0-BE13C9A21D1C}" name="acquisition_channel" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{193A8B1A-1FF7-4B1B-B684-F09EDE1E16D4}" name="total_customers" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{18E648D6-E390-46C4-8690-685CA751F4D9}" name="customers_with_loan" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{288A3F17-FF39-465C-A00D-1A42D7E8A815}" name="penetration_rate_pct %" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{67435B00-5F3D-4084-B4C0-BE13C9A21D1C}" name="acquisition_channel" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{193A8B1A-1FF7-4B1B-B684-F09EDE1E16D4}" name="total_customers" dataDxfId="46"/>
+    <tableColumn id="3" xr3:uid="{18E648D6-E390-46C4-8690-685CA751F4D9}" name="customers_with_loan" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{288A3F17-FF39-465C-A00D-1A42D7E8A815}" name="penetration_rate_pct %" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F473D1D7-6CAF-4854-8BAF-4A0C5284C9E9}" name="Table5" displayName="Table5" ref="B33:E35" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
-  <autoFilter ref="B33:E35" xr:uid="{F473D1D7-6CAF-4854-8BAF-4A0C5284C9E9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F473D1D7-6CAF-4854-8BAF-4A0C5284C9E9}" name="Table5" displayName="Table5" ref="B32:E34" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
+  <autoFilter ref="B32:E34" xr:uid="{F473D1D7-6CAF-4854-8BAF-4A0C5284C9E9}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0F8227EB-C728-4BAE-8F0D-4B987E1518D7}" name="loan_customers_with_valid_dsr" dataDxfId="52"/>
-    <tableColumn id="2" xr3:uid="{69E71CBB-4894-439A-9067-DEA8456C3D33}" name="customers_exceeding_1" dataDxfId="51"/>
-    <tableColumn id="3" xr3:uid="{92966840-2904-47F2-AE41-A9B8AB3AB910}" name="pct_exceeding_1" dataDxfId="50"/>
-    <tableColumn id="4" xr3:uid="{CBE0DC82-CE40-4CD1-B1CA-069196CF78EE}" name="total_lkr_exposure" dataDxfId="49"/>
+    <tableColumn id="1" xr3:uid="{0F8227EB-C728-4BAE-8F0D-4B987E1518D7}" name="loan_customers_with_valid_dsr" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{69E71CBB-4894-439A-9067-DEA8456C3D33}" name="customers_exceeding_1" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{92966840-2904-47F2-AE41-A9B8AB3AB910}" name="pct_exceeding_1" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{CBE0DC82-CE40-4CD1-B1CA-069196CF78EE}" name="total_lkr_exposure" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A94D5458-D48B-4C95-8855-88D5777C1635}" name="Table6" displayName="Table6" ref="B40:I253" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
-  <autoFilter ref="B40:I253" xr:uid="{A94D5458-D48B-4C95-8855-88D5777C1635}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A94D5458-D48B-4C95-8855-88D5777C1635}" name="Table6" displayName="Table6" ref="B39:I252" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36">
+  <autoFilter ref="B39:I252" xr:uid="{A94D5458-D48B-4C95-8855-88D5777C1635}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{39993F06-9C44-42F0-A989-EE0F52E339A0}" name="customer_id" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{E7FDBC6E-3798-4DFD-A86E-4E230D68D774}" name="customer_segment" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{5BA38347-7B56-4887-BE90-F3FF5C327B43}" name="district" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{0B16A70C-1727-4DC2-8AEB-A6378D99A114}" name="loan_type" dataDxfId="43"/>
-    <tableColumn id="5" xr3:uid="{1B17924E-9FE8-4E3C-BAD4-E8CF8A0D9073}" name="savings_balance" dataDxfId="42"/>
-    <tableColumn id="6" xr3:uid="{496C7A5C-27D1-481C-86BD-F6E878536784}" name="outstanding_loan_balance" dataDxfId="41"/>
-    <tableColumn id="7" xr3:uid="{58F5D9DC-7325-4EC8-BA03-A8029829A3CC}" name="debt_to_savings_ratio" dataDxfId="40"/>
-    <tableColumn id="8" xr3:uid="{51CFA383-1706-40B1-A4EC-63D443ACD9CC}" name="risk_flag" dataDxfId="39"/>
+    <tableColumn id="1" xr3:uid="{39993F06-9C44-42F0-A989-EE0F52E339A0}" name="customer_id" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{E7FDBC6E-3798-4DFD-A86E-4E230D68D774}" name="customer_segment" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{5BA38347-7B56-4887-BE90-F3FF5C327B43}" name="district" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{0B16A70C-1727-4DC2-8AEB-A6378D99A114}" name="loan_type" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{1B17924E-9FE8-4E3C-BAD4-E8CF8A0D9073}" name="savings_balance" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{496C7A5C-27D1-481C-86BD-F6E878536784}" name="outstanding_loan_balance" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{58F5D9DC-7325-4EC8-BA03-A8029829A3CC}" name="debt_to_savings_ratio" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{51CFA383-1706-40B1-A4EC-63D443ACD9CC}" name="risk_flag" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{17976B61-48C2-42BB-8A85-5547D3C8C049}" name="Table7" displayName="Table7" ref="B259:G263" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
-  <autoFilter ref="B259:G263" xr:uid="{17976B61-48C2-42BB-8A85-5547D3C8C049}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{17976B61-48C2-42BB-8A85-5547D3C8C049}" name="Table7" displayName="Table7" ref="B258:G262" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+  <autoFilter ref="B258:G262" xr:uid="{17976B61-48C2-42BB-8A85-5547D3C8C049}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{18487D9A-524E-4C1A-81DE-D6C11D6C9A85}" name="customer_segment" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{8071CB30-5A56-4D4E-B2AC-F08E3BAB6CD7}" name="total_loan_customers" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{8F0745C7-851F-493C-B710-F08768B2711E}" name="defaulted" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{3B339666-7B59-4A1A-A9B0-C05FC699D7C3}" name="delayed" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{C05DE78A-5667-41CC-BA51-BABBD7142B3D}" name="on_time" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{4DCC3E17-85B8-4BBA-B929-846943BAFCC6}" name="default_rate_pct %" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{18487D9A-524E-4C1A-81DE-D6C11D6C9A85}" name="customer_segment" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{8071CB30-5A56-4D4E-B2AC-F08E3BAB6CD7}" name="total_loan_customers" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{8F0745C7-851F-493C-B710-F08768B2711E}" name="defaulted" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{3B339666-7B59-4A1A-A9B0-C05FC699D7C3}" name="delayed" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{C05DE78A-5667-41CC-BA51-BABBD7142B3D}" name="on_time" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{4DCC3E17-85B8-4BBA-B929-846943BAFCC6}" name="default_rate_pct %" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A87D28F5-85A3-44F0-8C70-D42FD69C5451}" name="Table8" displayName="Table8" ref="B268:E272" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="B268:E272" xr:uid="{A87D28F5-85A3-44F0-8C70-D42FD69C5451}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A87D28F5-85A3-44F0-8C70-D42FD69C5451}" name="Table8" displayName="Table8" ref="B267:E271" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+  <autoFilter ref="B267:E271" xr:uid="{A87D28F5-85A3-44F0-8C70-D42FD69C5451}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{12C52A1E-9DAC-4556-BEEA-AEEAEDAB26BC}" name="loan_type" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{DCC2EB4E-0BFD-4A24-AB29-E5D9DE84832D}" name="total_loans" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{F0CA0D23-E32D-4232-876F-28C99AABADCF}" name="defaulted" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{081748BF-608A-40E1-AF08-3E636DD05D28}" name="default_rate_pct %" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{12C52A1E-9DAC-4556-BEEA-AEEAEDAB26BC}" name="loan_type" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{DCC2EB4E-0BFD-4A24-AB29-E5D9DE84832D}" name="total_loans" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{F0CA0D23-E32D-4232-876F-28C99AABADCF}" name="defaulted" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{081748BF-608A-40E1-AF08-3E636DD05D28}" name="default_rate_pct %" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{07291F89-0623-451A-8621-A6E14A9EE3B5}" name="Table9" displayName="Table9" ref="B277:E287" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="B277:E287" xr:uid="{07291F89-0623-451A-8621-A6E14A9EE3B5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{07291F89-0623-451A-8621-A6E14A9EE3B5}" name="Table9" displayName="Table9" ref="B276:E286" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="B276:E286" xr:uid="{07291F89-0623-451A-8621-A6E14A9EE3B5}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A9F51A40-F712-4960-9463-A51074FB2148}" name="district" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{DB93FD14-FA85-45AB-8671-1691356246E9}" name="total_loans" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{0C2B5F6C-0642-4B7D-A75D-270EC03ACC73}" name="defaulted" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{6D3D51B5-E9C6-40CF-9591-C23981EFA1ED}" name="default_rate_pct  %" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{A9F51A40-F712-4960-9463-A51074FB2148}" name="district" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{DB93FD14-FA85-45AB-8671-1691356246E9}" name="total_loans" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{0C2B5F6C-0642-4B7D-A75D-270EC03ACC73}" name="defaulted" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{6D3D51B5-E9C6-40CF-9591-C23981EFA1ED}" name="default_rate_pct  %" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{9781CE0C-E85C-4FCF-8D2C-82D072DF5E0D}" name="Table10" displayName="Table10" ref="B293:G305" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
-  <autoFilter ref="B293:G305" xr:uid="{9781CE0C-E85C-4FCF-8D2C-82D072DF5E0D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{9781CE0C-E85C-4FCF-8D2C-82D072DF5E0D}" name="Table10" displayName="Table10" ref="B292:G304" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="B292:G304" xr:uid="{9781CE0C-E85C-4FCF-8D2C-82D072DF5E0D}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{C0D7BC8E-8504-4597-802F-33FE6743B72F}" name="customer_segment" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{A02007F4-BA75-455D-8C37-6ECF6179BF91}" name="loan_type" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{4C08832A-F4BB-4641-B30B-A9A8B87B9183}" name="total_loans" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{3A71DDFC-EB7D-4D64-985C-D4BD6E748052}" name="defaulted" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{AD1D0527-5456-434E-BB67-67878F289576}" name="default_rate_pct  %" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{D54CC3B0-8B5D-41C5-858C-2D9D977E7ABB}" name="risk_flag" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{C0D7BC8E-8504-4597-802F-33FE6743B72F}" name="customer_segment" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{A02007F4-BA75-455D-8C37-6ECF6179BF91}" name="loan_type" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{4C08832A-F4BB-4641-B30B-A9A8B87B9183}" name="total_loans" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{3A71DDFC-EB7D-4D64-985C-D4BD6E748052}" name="defaulted" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{AD1D0527-5456-434E-BB67-67878F289576}" name="default_rate_pct  %" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{D54CC3B0-8B5D-41C5-858C-2D9D977E7ABB}" name="risk_flag" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1540,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:I305"/>
+  <dimension ref="B3:I304"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="7"/>
@@ -1657,172 +1659,198 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B21" s="5" t="s">
+    <row r="20" spans="2:5" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>268</v>
+        <v>11</v>
+      </c>
+      <c r="C23" s="2">
+        <v>117</v>
+      </c>
+      <c r="D23" s="2">
+        <v>56</v>
+      </c>
+      <c r="E23" s="2">
+        <v>47.9</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C24" s="2">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D24" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E24" s="2">
-        <v>47.9</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C25" s="2">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D25" s="2">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E25" s="2">
-        <v>44.2</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C26" s="2">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D26" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E26" s="2">
-        <v>41.5</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="2">
-        <v>131</v>
-      </c>
-      <c r="D27" s="2">
-        <v>54</v>
-      </c>
-      <c r="E27" s="2">
         <v>41.2</v>
       </c>
     </row>
-    <row r="31" spans="2:5" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B31" s="5" t="s">
+    <row r="30" spans="2:5" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="6"/>
+      <c r="C30" s="6"/>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="2">
+      <c r="B33" s="2">
         <v>212</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C33" s="2">
         <v>126</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D33" s="2">
         <v>59.4</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E33" s="4">
         <v>130101268.26000001</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B38" s="5" t="s">
+    <row r="37" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B37" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B39" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="7" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="F40" s="8">
+        <v>5945.01</v>
+      </c>
+      <c r="G40" s="8">
+        <v>795930.67</v>
+      </c>
+      <c r="H40" s="7">
+        <v>133.88</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F41" s="8">
-        <v>5945.01</v>
+        <v>7337.14</v>
       </c>
       <c r="G41" s="8">
-        <v>795930.67</v>
+        <v>578040.37</v>
       </c>
       <c r="H41" s="7">
-        <v>133.88</v>
+        <v>78.78</v>
       </c>
       <c r="I41" s="7" t="s">
         <v>31</v>
@@ -1830,7 +1858,7 @@
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>8</v>
@@ -1839,16 +1867,16 @@
         <v>33</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F42" s="8">
-        <v>7337.14</v>
+        <v>7411.39</v>
       </c>
       <c r="G42" s="8">
-        <v>578040.37</v>
+        <v>572624.68000000005</v>
       </c>
       <c r="H42" s="7">
-        <v>78.78</v>
+        <v>77.260000000000005</v>
       </c>
       <c r="I42" s="7" t="s">
         <v>31</v>
@@ -1856,10 +1884,10 @@
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>33</v>
@@ -1868,13 +1896,13 @@
         <v>30</v>
       </c>
       <c r="F43" s="8">
-        <v>7411.39</v>
+        <v>34701.81</v>
       </c>
       <c r="G43" s="8">
-        <v>572624.68000000005</v>
+        <v>1453320.53</v>
       </c>
       <c r="H43" s="7">
-        <v>77.260000000000005</v>
+        <v>41.88</v>
       </c>
       <c r="I43" s="7" t="s">
         <v>31</v>
@@ -1882,25 +1910,25 @@
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F44" s="8">
-        <v>34701.81</v>
+        <v>43546.19</v>
       </c>
       <c r="G44" s="8">
-        <v>1453320.53</v>
+        <v>1264320.82</v>
       </c>
       <c r="H44" s="7">
-        <v>41.88</v>
+        <v>29.03</v>
       </c>
       <c r="I44" s="7" t="s">
         <v>31</v>
@@ -1908,7 +1936,7 @@
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>8</v>
@@ -1920,13 +1948,13 @@
         <v>39</v>
       </c>
       <c r="F45" s="8">
-        <v>43546.19</v>
+        <v>33396.230000000003</v>
       </c>
       <c r="G45" s="8">
-        <v>1264320.82</v>
+        <v>913744.15</v>
       </c>
       <c r="H45" s="7">
-        <v>29.03</v>
+        <v>27.36</v>
       </c>
       <c r="I45" s="7" t="s">
         <v>31</v>
@@ -1934,25 +1962,25 @@
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>38</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F46" s="8">
-        <v>33396.230000000003</v>
+        <v>25630.03</v>
       </c>
       <c r="G46" s="8">
-        <v>913744.15</v>
+        <v>698529.95</v>
       </c>
       <c r="H46" s="7">
-        <v>27.36</v>
+        <v>27.25</v>
       </c>
       <c r="I46" s="7" t="s">
         <v>31</v>
@@ -1960,25 +1988,25 @@
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F47" s="8">
-        <v>25630.03</v>
+        <v>8161.03</v>
       </c>
       <c r="G47" s="8">
-        <v>698529.95</v>
+        <v>192636.95</v>
       </c>
       <c r="H47" s="7">
-        <v>27.25</v>
+        <v>23.6</v>
       </c>
       <c r="I47" s="7" t="s">
         <v>31</v>
@@ -1986,25 +2014,25 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>39</v>
       </c>
       <c r="F48" s="8">
-        <v>8161.03</v>
+        <v>91031.07</v>
       </c>
       <c r="G48" s="8">
-        <v>192636.95</v>
+        <v>2143396.6800000002</v>
       </c>
       <c r="H48" s="7">
-        <v>23.6</v>
+        <v>23.55</v>
       </c>
       <c r="I48" s="7" t="s">
         <v>31</v>
@@ -2012,25 +2040,25 @@
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B49" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F49" s="8">
-        <v>91031.07</v>
+        <v>75389.36</v>
       </c>
       <c r="G49" s="8">
-        <v>2143396.6800000002</v>
+        <v>1762089.51</v>
       </c>
       <c r="H49" s="7">
-        <v>23.55</v>
+        <v>23.37</v>
       </c>
       <c r="I49" s="7" t="s">
         <v>31</v>
@@ -2038,25 +2066,25 @@
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B50" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F50" s="8">
-        <v>75389.36</v>
+        <v>73151.509999999995</v>
       </c>
       <c r="G50" s="8">
-        <v>1762089.51</v>
+        <v>1659316.26</v>
       </c>
       <c r="H50" s="7">
-        <v>23.37</v>
+        <v>22.68</v>
       </c>
       <c r="I50" s="7" t="s">
         <v>31</v>
@@ -2064,25 +2092,25 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B51" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F51" s="8">
-        <v>73151.509999999995</v>
+        <v>64176.800000000003</v>
       </c>
       <c r="G51" s="8">
-        <v>1659316.26</v>
+        <v>1448399.4</v>
       </c>
       <c r="H51" s="7">
-        <v>22.68</v>
+        <v>22.57</v>
       </c>
       <c r="I51" s="7" t="s">
         <v>31</v>
@@ -2090,25 +2118,25 @@
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B52" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F52" s="8">
-        <v>64176.800000000003</v>
+        <v>79964.649999999994</v>
       </c>
       <c r="G52" s="8">
-        <v>1448399.4</v>
+        <v>1571161.43</v>
       </c>
       <c r="H52" s="7">
-        <v>22.57</v>
+        <v>19.649999999999999</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>31</v>
@@ -2116,25 +2144,25 @@
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B53" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F53" s="8">
-        <v>79964.649999999994</v>
+        <v>45696.87</v>
       </c>
       <c r="G53" s="8">
-        <v>1571161.43</v>
+        <v>896456.69</v>
       </c>
       <c r="H53" s="7">
-        <v>19.649999999999999</v>
+        <v>19.62</v>
       </c>
       <c r="I53" s="7" t="s">
         <v>31</v>
@@ -2142,25 +2170,25 @@
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B54" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F54" s="8">
-        <v>45696.87</v>
+        <v>42518.17</v>
       </c>
       <c r="G54" s="8">
-        <v>896456.69</v>
+        <v>826525.09</v>
       </c>
       <c r="H54" s="7">
-        <v>19.62</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="I54" s="7" t="s">
         <v>31</v>
@@ -2168,25 +2196,25 @@
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B55" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F55" s="8">
-        <v>42518.17</v>
+        <v>80903.899999999994</v>
       </c>
       <c r="G55" s="8">
-        <v>826525.09</v>
+        <v>1416901.94</v>
       </c>
       <c r="H55" s="7">
-        <v>19.440000000000001</v>
+        <v>17.510000000000002</v>
       </c>
       <c r="I55" s="7" t="s">
         <v>31</v>
@@ -2194,25 +2222,25 @@
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B56" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F56" s="8">
-        <v>80903.899999999994</v>
+        <v>14824.57</v>
       </c>
       <c r="G56" s="8">
-        <v>1416901.94</v>
+        <v>256156.01</v>
       </c>
       <c r="H56" s="7">
-        <v>17.510000000000002</v>
+        <v>17.28</v>
       </c>
       <c r="I56" s="7" t="s">
         <v>31</v>
@@ -2220,25 +2248,25 @@
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B57" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F57" s="8">
-        <v>14824.57</v>
+        <v>89425.38</v>
       </c>
       <c r="G57" s="8">
-        <v>256156.01</v>
+        <v>1440886.24</v>
       </c>
       <c r="H57" s="7">
-        <v>17.28</v>
+        <v>16.11</v>
       </c>
       <c r="I57" s="7" t="s">
         <v>31</v>
@@ -2246,25 +2274,25 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B58" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>38</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F58" s="8">
-        <v>89425.38</v>
+        <v>123359.03</v>
       </c>
       <c r="G58" s="8">
-        <v>1440886.24</v>
+        <v>1842211</v>
       </c>
       <c r="H58" s="7">
-        <v>16.11</v>
+        <v>14.93</v>
       </c>
       <c r="I58" s="7" t="s">
         <v>31</v>
@@ -2272,25 +2300,25 @@
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B59" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F59" s="8">
-        <v>123359.03</v>
+        <v>130733.71</v>
       </c>
       <c r="G59" s="8">
-        <v>1842211</v>
+        <v>1666360.98</v>
       </c>
       <c r="H59" s="7">
-        <v>14.93</v>
+        <v>12.75</v>
       </c>
       <c r="I59" s="7" t="s">
         <v>31</v>
@@ -2298,25 +2326,25 @@
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B60" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F60" s="8">
-        <v>130733.71</v>
+        <v>16624.71</v>
       </c>
       <c r="G60" s="8">
-        <v>1666360.98</v>
+        <v>206438.48</v>
       </c>
       <c r="H60" s="7">
-        <v>12.75</v>
+        <v>12.42</v>
       </c>
       <c r="I60" s="7" t="s">
         <v>31</v>
@@ -2324,25 +2352,25 @@
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B61" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F61" s="8">
-        <v>16624.71</v>
+        <v>78904.25</v>
       </c>
       <c r="G61" s="8">
-        <v>206438.48</v>
+        <v>933970.1</v>
       </c>
       <c r="H61" s="7">
-        <v>12.42</v>
+        <v>11.84</v>
       </c>
       <c r="I61" s="7" t="s">
         <v>31</v>
@@ -2350,25 +2378,25 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B62" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F62" s="8">
-        <v>78904.25</v>
+        <v>211198.96</v>
       </c>
       <c r="G62" s="8">
-        <v>933970.1</v>
+        <v>2346171.42</v>
       </c>
       <c r="H62" s="7">
-        <v>11.84</v>
+        <v>11.11</v>
       </c>
       <c r="I62" s="7" t="s">
         <v>31</v>
@@ -2376,25 +2404,25 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B63" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F63" s="8">
-        <v>211198.96</v>
+        <v>169361.11</v>
       </c>
       <c r="G63" s="8">
-        <v>2346171.42</v>
+        <v>1874755.11</v>
       </c>
       <c r="H63" s="7">
-        <v>11.11</v>
+        <v>11.07</v>
       </c>
       <c r="I63" s="7" t="s">
         <v>31</v>
@@ -2402,25 +2430,25 @@
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B64" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>64</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F64" s="8">
-        <v>169361.11</v>
+        <v>47259.98</v>
       </c>
       <c r="G64" s="8">
-        <v>1874755.11</v>
+        <v>507955.99</v>
       </c>
       <c r="H64" s="7">
-        <v>11.07</v>
+        <v>10.75</v>
       </c>
       <c r="I64" s="7" t="s">
         <v>31</v>
@@ -2428,25 +2456,25 @@
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B65" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F65" s="8">
-        <v>47259.98</v>
+        <v>64001.58</v>
       </c>
       <c r="G65" s="8">
-        <v>507955.99</v>
+        <v>652781.61</v>
       </c>
       <c r="H65" s="7">
-        <v>10.75</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="I65" s="7" t="s">
         <v>31</v>
@@ -2454,25 +2482,25 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B66" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F66" s="8">
-        <v>64001.58</v>
+        <v>69325.320000000007</v>
       </c>
       <c r="G66" s="8">
-        <v>652781.61</v>
+        <v>679200.7</v>
       </c>
       <c r="H66" s="7">
-        <v>10.199999999999999</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="I66" s="7" t="s">
         <v>31</v>
@@ -2480,25 +2508,22 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B67" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F67" s="8">
-        <v>69325.320000000007</v>
+        <v>113054.03</v>
       </c>
       <c r="G67" s="8">
-        <v>679200.7</v>
+        <v>1072378.6200000001</v>
       </c>
       <c r="H67" s="7">
-        <v>9.8000000000000007</v>
+        <v>9.49</v>
       </c>
       <c r="I67" s="7" t="s">
         <v>31</v>
@@ -2506,7 +2531,10 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B68" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>7</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>69</v>
@@ -2515,13 +2543,13 @@
         <v>30</v>
       </c>
       <c r="F68" s="8">
-        <v>113054.03</v>
+        <v>241898.82</v>
       </c>
       <c r="G68" s="8">
-        <v>1072378.6200000001</v>
+        <v>2259294.2200000002</v>
       </c>
       <c r="H68" s="7">
-        <v>9.49</v>
+        <v>9.34</v>
       </c>
       <c r="I68" s="7" t="s">
         <v>31</v>
@@ -2529,25 +2557,25 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B69" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C69" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F69" s="8">
-        <v>241898.82</v>
+        <v>120223.85</v>
       </c>
       <c r="G69" s="8">
-        <v>2259294.2200000002</v>
+        <v>1106135.8999999999</v>
       </c>
       <c r="H69" s="7">
-        <v>9.34</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="I69" s="7" t="s">
         <v>31</v>
@@ -2555,25 +2583,25 @@
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B70" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C70" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F70" s="8">
-        <v>120223.85</v>
+        <v>137368.67000000001</v>
       </c>
       <c r="G70" s="8">
-        <v>1106135.8999999999</v>
+        <v>1246397.49</v>
       </c>
       <c r="H70" s="7">
-        <v>9.1999999999999993</v>
+        <v>9.07</v>
       </c>
       <c r="I70" s="7" t="s">
         <v>31</v>
@@ -2581,25 +2609,25 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B71" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C71" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F71" s="8">
-        <v>137368.67000000001</v>
+        <v>44432.14</v>
       </c>
       <c r="G71" s="8">
-        <v>1246397.49</v>
+        <v>350946.05</v>
       </c>
       <c r="H71" s="7">
-        <v>9.07</v>
+        <v>7.9</v>
       </c>
       <c r="I71" s="7" t="s">
         <v>31</v>
@@ -2607,25 +2635,25 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B72" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F72" s="8">
-        <v>44432.14</v>
+        <v>92031.25</v>
       </c>
       <c r="G72" s="8">
-        <v>350946.05</v>
+        <v>723954.85</v>
       </c>
       <c r="H72" s="7">
-        <v>7.9</v>
+        <v>7.87</v>
       </c>
       <c r="I72" s="7" t="s">
         <v>31</v>
@@ -2633,25 +2661,25 @@
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B73" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C73" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F73" s="8">
-        <v>92031.25</v>
+        <v>96913.63</v>
       </c>
       <c r="G73" s="8">
-        <v>723954.85</v>
+        <v>732058.23</v>
       </c>
       <c r="H73" s="7">
-        <v>7.87</v>
+        <v>7.55</v>
       </c>
       <c r="I73" s="7" t="s">
         <v>31</v>
@@ -2659,25 +2687,22 @@
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B74" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F74" s="8">
-        <v>96913.63</v>
+        <v>140350.67000000001</v>
       </c>
       <c r="G74" s="8">
-        <v>732058.23</v>
+        <v>904769.88</v>
       </c>
       <c r="H74" s="7">
-        <v>7.55</v>
+        <v>6.45</v>
       </c>
       <c r="I74" s="7" t="s">
         <v>31</v>
@@ -2685,22 +2710,25 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B75" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F75" s="8">
-        <v>140350.67000000001</v>
+        <v>106706.85</v>
       </c>
       <c r="G75" s="8">
-        <v>904769.88</v>
+        <v>675380.7</v>
       </c>
       <c r="H75" s="7">
-        <v>6.45</v>
+        <v>6.33</v>
       </c>
       <c r="I75" s="7" t="s">
         <v>31</v>
@@ -2708,25 +2736,25 @@
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B76" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F76" s="8">
-        <v>106706.85</v>
+        <v>227638.22</v>
       </c>
       <c r="G76" s="8">
-        <v>675380.7</v>
+        <v>1360303.01</v>
       </c>
       <c r="H76" s="7">
-        <v>6.33</v>
+        <v>5.98</v>
       </c>
       <c r="I76" s="7" t="s">
         <v>31</v>
@@ -2734,25 +2762,25 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B77" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C77" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E77" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F77" s="8">
-        <v>227638.22</v>
+        <v>260615.7</v>
       </c>
       <c r="G77" s="8">
-        <v>1360303.01</v>
+        <v>1461148.51</v>
       </c>
       <c r="H77" s="7">
-        <v>5.98</v>
+        <v>5.61</v>
       </c>
       <c r="I77" s="7" t="s">
         <v>31</v>
@@ -2760,25 +2788,25 @@
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B78" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D78" s="7" t="s">
         <v>43</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F78" s="8">
-        <v>260615.7</v>
+        <v>15849.51</v>
       </c>
       <c r="G78" s="8">
-        <v>1461148.51</v>
+        <v>88692.12</v>
       </c>
       <c r="H78" s="7">
-        <v>5.61</v>
+        <v>5.6</v>
       </c>
       <c r="I78" s="7" t="s">
         <v>31</v>
@@ -2786,25 +2814,25 @@
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B79" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F79" s="8">
-        <v>15849.51</v>
+        <v>92638.5</v>
       </c>
       <c r="G79" s="8">
-        <v>88692.12</v>
+        <v>516992.52</v>
       </c>
       <c r="H79" s="7">
-        <v>5.6</v>
+        <v>5.58</v>
       </c>
       <c r="I79" s="7" t="s">
         <v>31</v>
@@ -2812,25 +2840,22 @@
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B80" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F80" s="8">
-        <v>92638.5</v>
+        <v>199730.37</v>
       </c>
       <c r="G80" s="8">
-        <v>516992.52</v>
+        <v>1076286.82</v>
       </c>
       <c r="H80" s="7">
-        <v>5.58</v>
+        <v>5.39</v>
       </c>
       <c r="I80" s="7" t="s">
         <v>31</v>
@@ -2838,22 +2863,25 @@
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B81" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>8</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F81" s="8">
-        <v>199730.37</v>
+        <v>141786.32999999999</v>
       </c>
       <c r="G81" s="8">
-        <v>1076286.82</v>
+        <v>727322.96</v>
       </c>
       <c r="H81" s="7">
-        <v>5.39</v>
+        <v>5.13</v>
       </c>
       <c r="I81" s="7" t="s">
         <v>31</v>
@@ -2861,25 +2889,25 @@
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B82" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F82" s="8">
-        <v>141786.32999999999</v>
+        <v>71448.3</v>
       </c>
       <c r="G82" s="8">
-        <v>727322.96</v>
+        <v>361623.58</v>
       </c>
       <c r="H82" s="7">
-        <v>5.13</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="I82" s="7" t="s">
         <v>31</v>
@@ -2887,10 +2915,10 @@
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B83" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D83" s="7" t="s">
         <v>29</v>
@@ -2899,13 +2927,13 @@
         <v>34</v>
       </c>
       <c r="F83" s="8">
-        <v>71448.3</v>
+        <v>49084.75</v>
       </c>
       <c r="G83" s="8">
-        <v>361623.58</v>
+        <v>226795.2</v>
       </c>
       <c r="H83" s="7">
-        <v>5.0599999999999996</v>
+        <v>4.62</v>
       </c>
       <c r="I83" s="7" t="s">
         <v>31</v>
@@ -2913,25 +2941,25 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B84" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F84" s="8">
-        <v>49084.75</v>
+        <v>485296.02</v>
       </c>
       <c r="G84" s="8">
-        <v>226795.2</v>
+        <v>2155708.9300000002</v>
       </c>
       <c r="H84" s="7">
-        <v>4.62</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="I84" s="7" t="s">
         <v>31</v>
@@ -2939,25 +2967,25 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B85" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C85" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F85" s="8">
-        <v>485296.02</v>
+        <v>574892.76</v>
       </c>
       <c r="G85" s="8">
-        <v>2155708.9300000002</v>
+        <v>2460698.36</v>
       </c>
       <c r="H85" s="7">
-        <v>4.4400000000000004</v>
+        <v>4.28</v>
       </c>
       <c r="I85" s="7" t="s">
         <v>31</v>
@@ -2965,25 +2993,25 @@
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B86" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C86" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F86" s="8">
-        <v>574892.76</v>
+        <v>300999.34000000003</v>
       </c>
       <c r="G86" s="8">
-        <v>2460698.36</v>
+        <v>1240728.46</v>
       </c>
       <c r="H86" s="7">
-        <v>4.28</v>
+        <v>4.12</v>
       </c>
       <c r="I86" s="7" t="s">
         <v>31</v>
@@ -2991,25 +3019,25 @@
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B87" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C87" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F87" s="8">
-        <v>300999.34000000003</v>
+        <v>490027.83</v>
       </c>
       <c r="G87" s="8">
-        <v>1240728.46</v>
+        <v>1956557.08</v>
       </c>
       <c r="H87" s="7">
-        <v>4.12</v>
+        <v>3.99</v>
       </c>
       <c r="I87" s="7" t="s">
         <v>31</v>
@@ -3017,25 +3045,25 @@
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B88" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F88" s="8">
-        <v>490027.83</v>
+        <v>88500.32</v>
       </c>
       <c r="G88" s="8">
-        <v>1956557.08</v>
+        <v>349194.91</v>
       </c>
       <c r="H88" s="7">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="I88" s="7" t="s">
         <v>31</v>
@@ -3043,25 +3071,25 @@
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B89" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="E89" s="7" t="s">
         <v>39</v>
       </c>
       <c r="F89" s="8">
-        <v>88500.32</v>
+        <v>140321.25</v>
       </c>
       <c r="G89" s="8">
-        <v>349194.91</v>
+        <v>544119.86</v>
       </c>
       <c r="H89" s="7">
-        <v>3.95</v>
+        <v>3.88</v>
       </c>
       <c r="I89" s="7" t="s">
         <v>31</v>
@@ -3069,25 +3097,25 @@
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B90" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F90" s="8">
-        <v>140321.25</v>
+        <v>556766.32999999996</v>
       </c>
       <c r="G90" s="8">
-        <v>544119.86</v>
+        <v>2124601.17</v>
       </c>
       <c r="H90" s="7">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="I90" s="7" t="s">
         <v>31</v>
@@ -3095,25 +3123,25 @@
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B91" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C91" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F91" s="8">
-        <v>556766.32999999996</v>
+        <v>268164.33</v>
       </c>
       <c r="G91" s="8">
-        <v>2124601.17</v>
+        <v>1005953.16</v>
       </c>
       <c r="H91" s="7">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="I91" s="7" t="s">
         <v>31</v>
@@ -3121,25 +3149,25 @@
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B92" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F92" s="8">
-        <v>268164.33</v>
+        <v>136050.79999999999</v>
       </c>
       <c r="G92" s="8">
-        <v>1005953.16</v>
+        <v>502294.34</v>
       </c>
       <c r="H92" s="7">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="I92" s="7" t="s">
         <v>31</v>
@@ -3147,25 +3175,25 @@
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B93" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F93" s="8">
-        <v>136050.79999999999</v>
+        <v>448866.68</v>
       </c>
       <c r="G93" s="8">
-        <v>502294.34</v>
+        <v>1597007.78</v>
       </c>
       <c r="H93" s="7">
-        <v>3.69</v>
+        <v>3.56</v>
       </c>
       <c r="I93" s="7" t="s">
         <v>31</v>
@@ -3173,25 +3201,25 @@
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B94" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="E94" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F94" s="8">
-        <v>448866.68</v>
+        <v>518812.48</v>
       </c>
       <c r="G94" s="8">
-        <v>1597007.78</v>
+        <v>1821070.63</v>
       </c>
       <c r="H94" s="7">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="I94" s="7" t="s">
         <v>31</v>
@@ -3199,25 +3227,25 @@
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B95" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E95" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F95" s="8">
-        <v>518812.48</v>
+        <v>60452.98</v>
       </c>
       <c r="G95" s="8">
-        <v>1821070.63</v>
+        <v>211551.33</v>
       </c>
       <c r="H95" s="7">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="I95" s="7" t="s">
         <v>31</v>
@@ -3225,25 +3253,25 @@
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B96" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C96" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F96" s="8">
-        <v>60452.98</v>
+        <v>398535.66</v>
       </c>
       <c r="G96" s="8">
-        <v>211551.33</v>
+        <v>1384978.29</v>
       </c>
       <c r="H96" s="7">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="I96" s="7" t="s">
         <v>31</v>
@@ -3251,25 +3279,25 @@
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B97" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C97" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F97" s="8">
-        <v>398535.66</v>
+        <v>345639.88</v>
       </c>
       <c r="G97" s="8">
-        <v>1384978.29</v>
+        <v>1185795.48</v>
       </c>
       <c r="H97" s="7">
-        <v>3.48</v>
+        <v>3.43</v>
       </c>
       <c r="I97" s="7" t="s">
         <v>31</v>
@@ -3277,25 +3305,25 @@
     </row>
     <row r="98" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B98" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C98" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F98" s="8">
-        <v>345639.88</v>
+        <v>71766.44</v>
       </c>
       <c r="G98" s="8">
-        <v>1185795.48</v>
+        <v>235790.27</v>
       </c>
       <c r="H98" s="7">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="I98" s="7" t="s">
         <v>31</v>
@@ -3303,25 +3331,25 @@
     </row>
     <row r="99" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B99" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C99" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F99" s="8">
-        <v>71766.44</v>
+        <v>510987.14</v>
       </c>
       <c r="G99" s="8">
-        <v>235790.27</v>
+        <v>1614280.31</v>
       </c>
       <c r="H99" s="7">
-        <v>3.29</v>
+        <v>3.16</v>
       </c>
       <c r="I99" s="7" t="s">
         <v>31</v>
@@ -3329,25 +3357,25 @@
     </row>
     <row r="100" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B100" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F100" s="8">
-        <v>510987.14</v>
+        <v>120674.59</v>
       </c>
       <c r="G100" s="8">
-        <v>1614280.31</v>
+        <v>378353.23</v>
       </c>
       <c r="H100" s="7">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="I100" s="7" t="s">
         <v>31</v>
@@ -3355,25 +3383,25 @@
     </row>
     <row r="101" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B101" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F101" s="8">
-        <v>120674.59</v>
+        <v>485199.04</v>
       </c>
       <c r="G101" s="8">
-        <v>378353.23</v>
+        <v>1518451.26</v>
       </c>
       <c r="H101" s="7">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="I101" s="7" t="s">
         <v>31</v>
@@ -3381,25 +3409,25 @@
     </row>
     <row r="102" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B102" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C102" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E102" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F102" s="8">
-        <v>485199.04</v>
+        <v>509209.49</v>
       </c>
       <c r="G102" s="8">
-        <v>1518451.26</v>
+        <v>1573227.83</v>
       </c>
       <c r="H102" s="7">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="I102" s="7" t="s">
         <v>31</v>
@@ -3407,25 +3435,25 @@
     </row>
     <row r="103" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B103" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E103" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F103" s="8">
-        <v>509209.49</v>
+        <v>133530.14000000001</v>
       </c>
       <c r="G103" s="8">
-        <v>1573227.83</v>
+        <v>402049</v>
       </c>
       <c r="H103" s="7">
-        <v>3.09</v>
+        <v>3.01</v>
       </c>
       <c r="I103" s="7" t="s">
         <v>31</v>
@@ -3433,25 +3461,25 @@
     </row>
     <row r="104" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B104" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="E104" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F104" s="8">
-        <v>133530.14000000001</v>
+        <v>498893.71</v>
       </c>
       <c r="G104" s="8">
-        <v>402049</v>
+        <v>1496033.75</v>
       </c>
       <c r="H104" s="7">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="I104" s="7" t="s">
         <v>31</v>
@@ -3459,22 +3487,22 @@
     </row>
     <row r="105" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B105" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F105" s="8">
-        <v>498893.71</v>
+        <v>262732.40000000002</v>
       </c>
       <c r="G105" s="8">
-        <v>1496033.75</v>
+        <v>787496.58</v>
       </c>
       <c r="H105" s="7">
         <v>3</v>
@@ -3485,25 +3513,25 @@
     </row>
     <row r="106" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B106" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C106" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E106" s="7" t="s">
         <v>39</v>
       </c>
       <c r="F106" s="8">
-        <v>262732.40000000002</v>
+        <v>667455.16</v>
       </c>
       <c r="G106" s="8">
-        <v>787496.58</v>
+        <v>1969202.15</v>
       </c>
       <c r="H106" s="7">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="I106" s="7" t="s">
         <v>31</v>
@@ -3511,7 +3539,7 @@
     </row>
     <row r="107" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B107" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C107" s="7" t="s">
         <v>7</v>
@@ -3520,16 +3548,16 @@
         <v>45</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F107" s="8">
-        <v>667455.16</v>
+        <v>615123.06999999995</v>
       </c>
       <c r="G107" s="8">
-        <v>1969202.15</v>
+        <v>1804357.63</v>
       </c>
       <c r="H107" s="7">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="I107" s="7" t="s">
         <v>31</v>
@@ -3537,25 +3565,25 @@
     </row>
     <row r="108" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B108" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C108" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F108" s="8">
-        <v>615123.06999999995</v>
+        <v>52020.49</v>
       </c>
       <c r="G108" s="8">
-        <v>1804357.63</v>
+        <v>148742.29</v>
       </c>
       <c r="H108" s="7">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="I108" s="7" t="s">
         <v>31</v>
@@ -3563,25 +3591,25 @@
     </row>
     <row r="109" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B109" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C109" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F109" s="8">
-        <v>52020.49</v>
+        <v>248590.94</v>
       </c>
       <c r="G109" s="8">
-        <v>148742.29</v>
+        <v>707487.27</v>
       </c>
       <c r="H109" s="7">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="I109" s="7" t="s">
         <v>31</v>
@@ -3589,22 +3617,22 @@
     </row>
     <row r="110" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B110" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C110" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F110" s="8">
-        <v>248590.94</v>
+        <v>374355.63</v>
       </c>
       <c r="G110" s="8">
-        <v>707487.27</v>
+        <v>1065589.1299999999</v>
       </c>
       <c r="H110" s="7">
         <v>2.85</v>
@@ -3615,25 +3643,25 @@
     </row>
     <row r="111" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B111" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C111" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F111" s="8">
-        <v>374355.63</v>
+        <v>482677.41</v>
       </c>
       <c r="G111" s="8">
-        <v>1065589.1299999999</v>
+        <v>1364330.88</v>
       </c>
       <c r="H111" s="7">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="I111" s="7" t="s">
         <v>31</v>
@@ -3641,25 +3669,25 @@
     </row>
     <row r="112" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B112" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F112" s="8">
-        <v>482677.41</v>
+        <v>134012.43</v>
       </c>
       <c r="G112" s="8">
-        <v>1364330.88</v>
+        <v>359284.56</v>
       </c>
       <c r="H112" s="7">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="I112" s="7" t="s">
         <v>31</v>
@@ -3667,25 +3695,25 @@
     </row>
     <row r="113" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B113" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F113" s="8">
-        <v>134012.43</v>
+        <v>359594.4</v>
       </c>
       <c r="G113" s="8">
-        <v>359284.56</v>
+        <v>960258.15</v>
       </c>
       <c r="H113" s="7">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="I113" s="7" t="s">
         <v>31</v>
@@ -3693,22 +3721,22 @@
     </row>
     <row r="114" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B114" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C114" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F114" s="8">
-        <v>359594.4</v>
+        <v>587368.46</v>
       </c>
       <c r="G114" s="8">
-        <v>960258.15</v>
+        <v>1569390.53</v>
       </c>
       <c r="H114" s="7">
         <v>2.67</v>
@@ -3719,25 +3747,25 @@
     </row>
     <row r="115" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B115" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F115" s="8">
-        <v>587368.46</v>
+        <v>85217.43</v>
       </c>
       <c r="G115" s="8">
-        <v>1569390.53</v>
+        <v>220632.73</v>
       </c>
       <c r="H115" s="7">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="I115" s="7" t="s">
         <v>31</v>
@@ -3745,25 +3773,25 @@
     </row>
     <row r="116" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B116" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F116" s="8">
-        <v>85217.43</v>
+        <v>294377.18</v>
       </c>
       <c r="G116" s="8">
-        <v>220632.73</v>
+        <v>757796.13</v>
       </c>
       <c r="H116" s="7">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="I116" s="7" t="s">
         <v>31</v>
@@ -3771,25 +3799,25 @@
     </row>
     <row r="117" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B117" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F117" s="8">
-        <v>294377.18</v>
+        <v>54434.2</v>
       </c>
       <c r="G117" s="8">
-        <v>757796.13</v>
+        <v>138490.74</v>
       </c>
       <c r="H117" s="7">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="I117" s="7" t="s">
         <v>31</v>
@@ -3797,22 +3825,22 @@
     </row>
     <row r="118" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B118" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C118" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F118" s="8">
-        <v>54434.2</v>
+        <v>432090.61</v>
       </c>
       <c r="G118" s="8">
-        <v>138490.74</v>
+        <v>1098945.3400000001</v>
       </c>
       <c r="H118" s="7">
         <v>2.54</v>
@@ -3823,25 +3851,25 @@
     </row>
     <row r="119" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B119" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F119" s="8">
-        <v>432090.61</v>
+        <v>685386.63</v>
       </c>
       <c r="G119" s="8">
-        <v>1098945.3400000001</v>
+        <v>1698478.51</v>
       </c>
       <c r="H119" s="7">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="I119" s="7" t="s">
         <v>31</v>
@@ -3849,25 +3877,25 @@
     </row>
     <row r="120" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B120" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C120" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E120" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F120" s="8">
-        <v>685386.63</v>
+        <v>190875.71</v>
       </c>
       <c r="G120" s="8">
-        <v>1698478.51</v>
+        <v>470553.44</v>
       </c>
       <c r="H120" s="7">
-        <v>2.48</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="I120" s="7" t="s">
         <v>31</v>
@@ -3875,7 +3903,7 @@
     </row>
     <row r="121" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B121" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>7</v>
@@ -3884,16 +3912,16 @@
         <v>45</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F121" s="8">
-        <v>190875.71</v>
+        <v>756483.71</v>
       </c>
       <c r="G121" s="8">
-        <v>470553.44</v>
+        <v>1806849.6</v>
       </c>
       <c r="H121" s="7">
-        <v>2.4700000000000002</v>
+        <v>2.39</v>
       </c>
       <c r="I121" s="7" t="s">
         <v>31</v>
@@ -3901,25 +3929,25 @@
     </row>
     <row r="122" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B122" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F122" s="8">
-        <v>756483.71</v>
+        <v>410292.58</v>
       </c>
       <c r="G122" s="8">
-        <v>1806849.6</v>
+        <v>933511.36</v>
       </c>
       <c r="H122" s="7">
-        <v>2.39</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="I122" s="7" t="s">
         <v>31</v>
@@ -3927,25 +3955,25 @@
     </row>
     <row r="123" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B123" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C123" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F123" s="8">
-        <v>410292.58</v>
+        <v>648810.81000000006</v>
       </c>
       <c r="G123" s="8">
-        <v>933511.36</v>
+        <v>1457031.07</v>
       </c>
       <c r="H123" s="7">
-        <v>2.2799999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="I123" s="7" t="s">
         <v>31</v>
@@ -3953,25 +3981,25 @@
     </row>
     <row r="124" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B124" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C124" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="E124" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F124" s="8">
-        <v>648810.81000000006</v>
+        <v>658449.18000000005</v>
       </c>
       <c r="G124" s="8">
-        <v>1457031.07</v>
+        <v>1454776.81</v>
       </c>
       <c r="H124" s="7">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="I124" s="7" t="s">
         <v>31</v>
@@ -3979,25 +4007,25 @@
     </row>
     <row r="125" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B125" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C125" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="E125" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F125" s="8">
-        <v>658449.18000000005</v>
+        <v>657958.96</v>
       </c>
       <c r="G125" s="8">
-        <v>1454776.81</v>
+        <v>1444075</v>
       </c>
       <c r="H125" s="7">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="I125" s="7" t="s">
         <v>31</v>
@@ -4005,22 +4033,22 @@
     </row>
     <row r="126" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B126" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C126" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E126" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F126" s="8">
-        <v>657958.96</v>
+        <v>398643.69</v>
       </c>
       <c r="G126" s="8">
-        <v>1444075</v>
+        <v>874374.11</v>
       </c>
       <c r="H126" s="7">
         <v>2.19</v>
@@ -4031,25 +4059,25 @@
     </row>
     <row r="127" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B127" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C127" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F127" s="8">
-        <v>398643.69</v>
+        <v>709257.67</v>
       </c>
       <c r="G127" s="8">
-        <v>874374.11</v>
+        <v>1477483.41</v>
       </c>
       <c r="H127" s="7">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="I127" s="7" t="s">
         <v>31</v>
@@ -4057,10 +4085,10 @@
     </row>
     <row r="128" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B128" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D128" s="7" t="s">
         <v>45</v>
@@ -4069,13 +4097,13 @@
         <v>30</v>
       </c>
       <c r="F128" s="8">
-        <v>709257.67</v>
+        <v>102344.67</v>
       </c>
       <c r="G128" s="8">
-        <v>1477483.41</v>
+        <v>210688.1</v>
       </c>
       <c r="H128" s="7">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I128" s="7" t="s">
         <v>31</v>
@@ -4083,25 +4111,25 @@
     </row>
     <row r="129" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B129" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F129" s="8">
-        <v>102344.67</v>
+        <v>255151.61</v>
       </c>
       <c r="G129" s="8">
-        <v>210688.1</v>
+        <v>520443.36</v>
       </c>
       <c r="H129" s="7">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I129" s="7" t="s">
         <v>31</v>
@@ -4109,25 +4137,25 @@
     </row>
     <row r="130" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B130" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D130" s="7" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F130" s="8">
-        <v>255151.61</v>
+        <v>368721</v>
       </c>
       <c r="G130" s="8">
-        <v>520443.36</v>
+        <v>748085.08</v>
       </c>
       <c r="H130" s="7">
-        <v>2.04</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="I130" s="7" t="s">
         <v>31</v>
@@ -4135,25 +4163,25 @@
     </row>
     <row r="131" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B131" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F131" s="8">
-        <v>368721</v>
+        <v>80431.38</v>
       </c>
       <c r="G131" s="8">
-        <v>748085.08</v>
+        <v>161304.87</v>
       </c>
       <c r="H131" s="7">
-        <v>2.0299999999999998</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="I131" s="7" t="s">
         <v>31</v>
@@ -4161,25 +4189,25 @@
     </row>
     <row r="132" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B132" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F132" s="8">
-        <v>80431.38</v>
+        <v>571700.74</v>
       </c>
       <c r="G132" s="8">
-        <v>161304.87</v>
+        <v>1145802.8799999999</v>
       </c>
       <c r="H132" s="7">
-        <v>2.0099999999999998</v>
+        <v>2</v>
       </c>
       <c r="I132" s="7" t="s">
         <v>31</v>
@@ -4187,51 +4215,51 @@
     </row>
     <row r="133" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B133" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F133" s="8">
-        <v>571700.74</v>
+        <v>725957.05</v>
       </c>
       <c r="G133" s="8">
-        <v>1145802.8799999999</v>
+        <v>1439493.54</v>
       </c>
       <c r="H133" s="7">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>31</v>
+        <v>137</v>
       </c>
     </row>
     <row r="134" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B134" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D134" s="7" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F134" s="8">
-        <v>725957.05</v>
+        <v>567011.51</v>
       </c>
       <c r="G134" s="8">
-        <v>1439493.54</v>
+        <v>1109798.57</v>
       </c>
       <c r="H134" s="7">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="I134" s="7" t="s">
         <v>137</v>
@@ -4239,25 +4267,25 @@
     </row>
     <row r="135" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B135" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F135" s="8">
-        <v>567011.51</v>
+        <v>636588.51</v>
       </c>
       <c r="G135" s="8">
-        <v>1109798.57</v>
+        <v>1221046.17</v>
       </c>
       <c r="H135" s="7">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="I135" s="7" t="s">
         <v>137</v>
@@ -4265,25 +4293,25 @@
     </row>
     <row r="136" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B136" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F136" s="8">
-        <v>636588.51</v>
+        <v>717908.62</v>
       </c>
       <c r="G136" s="8">
-        <v>1221046.17</v>
+        <v>1372143.19</v>
       </c>
       <c r="H136" s="7">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="I136" s="7" t="s">
         <v>137</v>
@@ -4291,25 +4319,25 @@
     </row>
     <row r="137" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B137" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C137" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F137" s="8">
-        <v>717908.62</v>
+        <v>428773.47</v>
       </c>
       <c r="G137" s="8">
-        <v>1372143.19</v>
+        <v>789183.07</v>
       </c>
       <c r="H137" s="7">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="I137" s="7" t="s">
         <v>137</v>
@@ -4317,25 +4345,25 @@
     </row>
     <row r="138" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B138" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C138" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F138" s="8">
-        <v>428773.47</v>
+        <v>563564.82999999996</v>
       </c>
       <c r="G138" s="8">
-        <v>789183.07</v>
+        <v>1029042.58</v>
       </c>
       <c r="H138" s="7">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="I138" s="7" t="s">
         <v>137</v>
@@ -4343,25 +4371,25 @@
     </row>
     <row r="139" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B139" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C139" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F139" s="8">
-        <v>563564.82999999996</v>
+        <v>777279.19</v>
       </c>
       <c r="G139" s="8">
-        <v>1029042.58</v>
+        <v>1412207.02</v>
       </c>
       <c r="H139" s="7">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="I139" s="7" t="s">
         <v>137</v>
@@ -4369,25 +4397,25 @@
     </row>
     <row r="140" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B140" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C140" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F140" s="8">
-        <v>777279.19</v>
+        <v>596931.13</v>
       </c>
       <c r="G140" s="8">
-        <v>1412207.02</v>
+        <v>1070686.6399999999</v>
       </c>
       <c r="H140" s="7">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="I140" s="7" t="s">
         <v>137</v>
@@ -4395,22 +4423,22 @@
     </row>
     <row r="141" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B141" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C141" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F141" s="8">
-        <v>596931.13</v>
+        <v>483354</v>
       </c>
       <c r="G141" s="8">
-        <v>1070686.6399999999</v>
+        <v>862987.83</v>
       </c>
       <c r="H141" s="7">
         <v>1.79</v>
@@ -4421,25 +4449,25 @@
     </row>
     <row r="142" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B142" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F142" s="8">
-        <v>483354</v>
+        <v>1053396.3400000001</v>
       </c>
       <c r="G142" s="8">
-        <v>862987.83</v>
+        <v>1864546.97</v>
       </c>
       <c r="H142" s="7">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="I142" s="7" t="s">
         <v>137</v>
@@ -4447,25 +4475,25 @@
     </row>
     <row r="143" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B143" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F143" s="8">
-        <v>1053396.3400000001</v>
+        <v>305029.34999999998</v>
       </c>
       <c r="G143" s="8">
-        <v>1864546.97</v>
+        <v>518122.57</v>
       </c>
       <c r="H143" s="7">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="I143" s="7" t="s">
         <v>137</v>
@@ -4473,7 +4501,7 @@
     </row>
     <row r="144" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B144" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C144" s="7" t="s">
         <v>7</v>
@@ -4482,13 +4510,13 @@
         <v>84</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F144" s="8">
-        <v>305029.34999999998</v>
+        <v>701681.48</v>
       </c>
       <c r="G144" s="8">
-        <v>518122.57</v>
+        <v>1193574.28</v>
       </c>
       <c r="H144" s="7">
         <v>1.7</v>
@@ -4499,25 +4527,25 @@
     </row>
     <row r="145" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B145" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C145" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F145" s="8">
-        <v>701681.48</v>
+        <v>119590.99</v>
       </c>
       <c r="G145" s="8">
-        <v>1193574.28</v>
+        <v>200490.92</v>
       </c>
       <c r="H145" s="7">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="I145" s="7" t="s">
         <v>137</v>
@@ -4525,25 +4553,25 @@
     </row>
     <row r="146" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B146" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C146" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F146" s="8">
-        <v>119590.99</v>
+        <v>562847.61</v>
       </c>
       <c r="G146" s="8">
-        <v>200490.92</v>
+        <v>938700.31</v>
       </c>
       <c r="H146" s="7">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="I146" s="7" t="s">
         <v>137</v>
@@ -4551,25 +4579,25 @@
     </row>
     <row r="147" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B147" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C147" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F147" s="8">
-        <v>562847.61</v>
+        <v>728560.93</v>
       </c>
       <c r="G147" s="8">
-        <v>938700.31</v>
+        <v>1212667.6599999999</v>
       </c>
       <c r="H147" s="7">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="I147" s="7" t="s">
         <v>137</v>
@@ -4577,7 +4605,7 @@
     </row>
     <row r="148" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B148" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C148" s="7" t="s">
         <v>7</v>
@@ -4586,16 +4614,16 @@
         <v>38</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F148" s="8">
-        <v>728560.93</v>
+        <v>453534.8</v>
       </c>
       <c r="G148" s="8">
-        <v>1212667.6599999999</v>
+        <v>731627.55</v>
       </c>
       <c r="H148" s="7">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="I148" s="7" t="s">
         <v>137</v>
@@ -4603,25 +4631,25 @@
     </row>
     <row r="149" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B149" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C149" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F149" s="8">
-        <v>453534.8</v>
+        <v>287501.23</v>
       </c>
       <c r="G149" s="8">
-        <v>731627.55</v>
+        <v>459437.6</v>
       </c>
       <c r="H149" s="7">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="I149" s="7" t="s">
         <v>137</v>
@@ -4629,25 +4657,25 @@
     </row>
     <row r="150" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B150" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C150" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F150" s="8">
-        <v>287501.23</v>
+        <v>536036.34</v>
       </c>
       <c r="G150" s="8">
-        <v>459437.6</v>
+        <v>818164.22</v>
       </c>
       <c r="H150" s="7">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="I150" s="7" t="s">
         <v>137</v>
@@ -4655,25 +4683,25 @@
     </row>
     <row r="151" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B151" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C151" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F151" s="8">
-        <v>536036.34</v>
+        <v>691079.25</v>
       </c>
       <c r="G151" s="8">
-        <v>818164.22</v>
+        <v>1052688.19</v>
       </c>
       <c r="H151" s="7">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="I151" s="7" t="s">
         <v>137</v>
@@ -4681,7 +4709,7 @@
     </row>
     <row r="152" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B152" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C152" s="7" t="s">
         <v>7</v>
@@ -4693,10 +4721,10 @@
         <v>30</v>
       </c>
       <c r="F152" s="8">
-        <v>691079.25</v>
+        <v>562028.84</v>
       </c>
       <c r="G152" s="8">
-        <v>1052688.19</v>
+        <v>854891.66</v>
       </c>
       <c r="H152" s="7">
         <v>1.52</v>
@@ -4707,25 +4735,25 @@
     </row>
     <row r="153" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B153" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="E153" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F153" s="8">
-        <v>562028.84</v>
+        <v>988359.89</v>
       </c>
       <c r="G153" s="8">
-        <v>854891.66</v>
+        <v>1493942.9</v>
       </c>
       <c r="H153" s="7">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="I153" s="7" t="s">
         <v>137</v>
@@ -4733,25 +4761,25 @@
     </row>
     <row r="154" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B154" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F154" s="8">
-        <v>988359.89</v>
+        <v>791159.43</v>
       </c>
       <c r="G154" s="8">
-        <v>1493942.9</v>
+        <v>1184875.7</v>
       </c>
       <c r="H154" s="7">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I154" s="7" t="s">
         <v>137</v>
@@ -4759,25 +4787,25 @@
     </row>
     <row r="155" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B155" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C155" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="E155" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F155" s="8">
-        <v>791159.43</v>
+        <v>756041.42</v>
       </c>
       <c r="G155" s="8">
-        <v>1184875.7</v>
+        <v>1049350.19</v>
       </c>
       <c r="H155" s="7">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="I155" s="7" t="s">
         <v>137</v>
@@ -4785,25 +4813,25 @@
     </row>
     <row r="156" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B156" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C156" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D156" s="7" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F156" s="8">
-        <v>756041.42</v>
+        <v>624812.26</v>
       </c>
       <c r="G156" s="8">
-        <v>1049350.19</v>
+        <v>848055.85</v>
       </c>
       <c r="H156" s="7">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="I156" s="7" t="s">
         <v>137</v>
@@ -4811,25 +4839,25 @@
     </row>
     <row r="157" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B157" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D157" s="7" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="E157" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F157" s="8">
-        <v>624812.26</v>
+        <v>104484.14</v>
       </c>
       <c r="G157" s="8">
-        <v>848055.85</v>
+        <v>137994.73000000001</v>
       </c>
       <c r="H157" s="7">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="I157" s="7" t="s">
         <v>137</v>
@@ -4837,25 +4865,25 @@
     </row>
     <row r="158" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B158" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D158" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E158" s="7" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F158" s="8">
-        <v>104484.14</v>
+        <v>1300731.03</v>
       </c>
       <c r="G158" s="8">
-        <v>137994.73000000001</v>
+        <v>1664271.88</v>
       </c>
       <c r="H158" s="7">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="I158" s="7" t="s">
         <v>137</v>
@@ -4863,22 +4891,22 @@
     </row>
     <row r="159" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B159" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="E159" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F159" s="8">
-        <v>1300731.03</v>
+        <v>540677.71</v>
       </c>
       <c r="G159" s="8">
-        <v>1664271.88</v>
+        <v>693059.77</v>
       </c>
       <c r="H159" s="7">
         <v>1.28</v>
@@ -4889,25 +4917,25 @@
     </row>
     <row r="160" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B160" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C160" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E160" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F160" s="8">
-        <v>540677.71</v>
+        <v>525574.67000000004</v>
       </c>
       <c r="G160" s="8">
-        <v>693059.77</v>
+        <v>633679.93000000005</v>
       </c>
       <c r="H160" s="7">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="I160" s="7" t="s">
         <v>137</v>
@@ -4915,10 +4943,10 @@
     </row>
     <row r="161" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B161" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D161" s="7" t="s">
         <v>64</v>
@@ -4927,13 +4955,13 @@
         <v>39</v>
       </c>
       <c r="F161" s="8">
-        <v>525574.67000000004</v>
+        <v>115482.93</v>
       </c>
       <c r="G161" s="8">
-        <v>633679.93000000005</v>
+        <v>134529.54999999999</v>
       </c>
       <c r="H161" s="7">
-        <v>1.21</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="I161" s="7" t="s">
         <v>137</v>
@@ -4941,25 +4969,25 @@
     </row>
     <row r="162" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B162" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="E162" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F162" s="8">
-        <v>115482.93</v>
+        <v>984577.23</v>
       </c>
       <c r="G162" s="8">
-        <v>134529.54999999999</v>
+        <v>1136642.32</v>
       </c>
       <c r="H162" s="7">
-        <v>1.1599999999999999</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="I162" s="7" t="s">
         <v>137</v>
@@ -4967,25 +4995,25 @@
     </row>
     <row r="163" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B163" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="E163" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F163" s="8">
-        <v>984577.23</v>
+        <v>487957.63</v>
       </c>
       <c r="G163" s="8">
-        <v>1136642.32</v>
+        <v>551658.91</v>
       </c>
       <c r="H163" s="7">
-        <v>1.1499999999999999</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="I163" s="7" t="s">
         <v>137</v>
@@ -4993,25 +5021,25 @@
     </row>
     <row r="164" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B164" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="E164" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F164" s="8">
-        <v>487957.63</v>
+        <v>1224070.23</v>
       </c>
       <c r="G164" s="8">
-        <v>551658.91</v>
+        <v>1311494.03</v>
       </c>
       <c r="H164" s="7">
-        <v>1.1299999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="I164" s="7" t="s">
         <v>137</v>
@@ -5019,25 +5047,25 @@
     </row>
     <row r="165" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B165" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D165" s="7" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F165" s="8">
-        <v>1224070.23</v>
+        <v>495570.73</v>
       </c>
       <c r="G165" s="8">
-        <v>1311494.03</v>
+        <v>505541.4</v>
       </c>
       <c r="H165" s="7">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="I165" s="7" t="s">
         <v>137</v>
@@ -5045,51 +5073,51 @@
     </row>
     <row r="166" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B166" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C166" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D166" s="7" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E166" s="7" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F166" s="8">
-        <v>495570.73</v>
+        <v>236582.28</v>
       </c>
       <c r="G166" s="8">
-        <v>505541.4</v>
+        <v>233369.37</v>
       </c>
       <c r="H166" s="7">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
     </row>
     <row r="167" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B167" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C167" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="E167" s="7" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F167" s="8">
-        <v>236582.28</v>
+        <v>774396</v>
       </c>
       <c r="G167" s="8">
-        <v>233369.37</v>
+        <v>739557.51</v>
       </c>
       <c r="H167" s="7">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="I167" s="7" t="s">
         <v>171</v>
@@ -5097,25 +5125,25 @@
     </row>
     <row r="168" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B168" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C168" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D168" s="7" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="E168" s="7" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F168" s="8">
-        <v>774396</v>
+        <v>743711.7</v>
       </c>
       <c r="G168" s="8">
-        <v>739557.51</v>
+        <v>699881.94</v>
       </c>
       <c r="H168" s="7">
-        <v>0.96</v>
+        <v>0.94</v>
       </c>
       <c r="I168" s="7" t="s">
         <v>171</v>
@@ -5123,25 +5151,25 @@
     </row>
     <row r="169" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B169" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C169" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D169" s="7" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="E169" s="7" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F169" s="8">
-        <v>743711.7</v>
+        <v>299699.37</v>
       </c>
       <c r="G169" s="8">
-        <v>699881.94</v>
+        <v>280006.3</v>
       </c>
       <c r="H169" s="7">
-        <v>0.94</v>
+        <v>0.93</v>
       </c>
       <c r="I169" s="7" t="s">
         <v>171</v>
@@ -5149,25 +5177,25 @@
     </row>
     <row r="170" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B170" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C170" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D170" s="7" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E170" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F170" s="8">
-        <v>299699.37</v>
+        <v>543731.41</v>
       </c>
       <c r="G170" s="8">
-        <v>280006.3</v>
+        <v>495899.19</v>
       </c>
       <c r="H170" s="7">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="I170" s="7" t="s">
         <v>171</v>
@@ -5175,25 +5203,25 @@
     </row>
     <row r="171" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B171" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C171" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D171" s="7" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="E171" s="7" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F171" s="8">
-        <v>543731.41</v>
+        <v>791317.34</v>
       </c>
       <c r="G171" s="8">
-        <v>495899.19</v>
+        <v>696962.26</v>
       </c>
       <c r="H171" s="7">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="I171" s="7" t="s">
         <v>171</v>
@@ -5201,25 +5229,25 @@
     </row>
     <row r="172" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B172" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C172" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D172" s="7" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="E172" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F172" s="8">
-        <v>791317.34</v>
+        <v>575183.44999999995</v>
       </c>
       <c r="G172" s="8">
-        <v>696962.26</v>
+        <v>492669.91</v>
       </c>
       <c r="H172" s="7">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="I172" s="7" t="s">
         <v>171</v>
@@ -5227,25 +5255,25 @@
     </row>
     <row r="173" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B173" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C173" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D173" s="7" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="E173" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F173" s="8">
-        <v>575183.44999999995</v>
+        <v>379253.6</v>
       </c>
       <c r="G173" s="8">
-        <v>492669.91</v>
+        <v>312405.75</v>
       </c>
       <c r="H173" s="7">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="I173" s="7" t="s">
         <v>171</v>
@@ -5253,22 +5281,19 @@
     </row>
     <row r="174" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B174" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C174" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D174" s="7" t="s">
-        <v>55</v>
-      </c>
       <c r="E174" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F174" s="8">
-        <v>379253.6</v>
+        <v>523550.27</v>
       </c>
       <c r="G174" s="8">
-        <v>312405.75</v>
+        <v>431117.28</v>
       </c>
       <c r="H174" s="7">
         <v>0.82</v>
@@ -5279,22 +5304,25 @@
     </row>
     <row r="175" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B175" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="E175" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F175" s="8">
-        <v>523550.27</v>
+        <v>1355940.09</v>
       </c>
       <c r="G175" s="8">
-        <v>431117.28</v>
+        <v>1100207.08</v>
       </c>
       <c r="H175" s="7">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="I175" s="7" t="s">
         <v>171</v>
@@ -5302,22 +5330,22 @@
     </row>
     <row r="176" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B176" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C176" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D176" s="7" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="E176" s="7" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F176" s="8">
-        <v>1355940.09</v>
+        <v>1267488.23</v>
       </c>
       <c r="G176" s="8">
-        <v>1100207.08</v>
+        <v>1030916.54</v>
       </c>
       <c r="H176" s="7">
         <v>0.81</v>
@@ -5328,25 +5356,25 @@
     </row>
     <row r="177" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B177" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D177" s="7" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F177" s="8">
-        <v>1267488.23</v>
+        <v>485054.54</v>
       </c>
       <c r="G177" s="8">
-        <v>1030916.54</v>
+        <v>385469.83</v>
       </c>
       <c r="H177" s="7">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="I177" s="7" t="s">
         <v>171</v>
@@ -5354,25 +5382,25 @@
     </row>
     <row r="178" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B178" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C178" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D178" s="7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F178" s="8">
-        <v>485054.54</v>
+        <v>388603.23</v>
       </c>
       <c r="G178" s="8">
-        <v>385469.83</v>
+        <v>295905.40999999997</v>
       </c>
       <c r="H178" s="7">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="I178" s="7" t="s">
         <v>171</v>
@@ -5380,25 +5408,25 @@
     </row>
     <row r="179" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B179" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D179" s="7" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F179" s="8">
-        <v>388603.23</v>
+        <v>26618.959999999999</v>
       </c>
       <c r="G179" s="8">
-        <v>295905.40999999997</v>
+        <v>19572.11</v>
       </c>
       <c r="H179" s="7">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="I179" s="7" t="s">
         <v>171</v>
@@ -5406,25 +5434,25 @@
     </row>
     <row r="180" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B180" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C180" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D180" s="7" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F180" s="8">
-        <v>26618.959999999999</v>
+        <v>784798.29</v>
       </c>
       <c r="G180" s="8">
-        <v>19572.11</v>
+        <v>551780.79</v>
       </c>
       <c r="H180" s="7">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="I180" s="7" t="s">
         <v>171</v>
@@ -5432,7 +5460,7 @@
     </row>
     <row r="181" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B181" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C181" s="7" t="s">
         <v>7</v>
@@ -5441,13 +5469,13 @@
         <v>43</v>
       </c>
       <c r="E181" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F181" s="8">
-        <v>784798.29</v>
+        <v>785300.44</v>
       </c>
       <c r="G181" s="8">
-        <v>551780.79</v>
+        <v>553375.98</v>
       </c>
       <c r="H181" s="7">
         <v>0.7</v>
@@ -5458,25 +5486,25 @@
     </row>
     <row r="182" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B182" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C182" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E182" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F182" s="8">
-        <v>785300.44</v>
+        <v>248909.37</v>
       </c>
       <c r="G182" s="8">
-        <v>553375.98</v>
+        <v>156871.97</v>
       </c>
       <c r="H182" s="7">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="I182" s="7" t="s">
         <v>171</v>
@@ -5484,22 +5512,22 @@
     </row>
     <row r="183" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B183" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C183" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D183" s="7" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="E183" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F183" s="8">
-        <v>248909.37</v>
+        <v>130924.77</v>
       </c>
       <c r="G183" s="8">
-        <v>156871.97</v>
+        <v>81938.42</v>
       </c>
       <c r="H183" s="7">
         <v>0.63</v>
@@ -5510,25 +5538,25 @@
     </row>
     <row r="184" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B184" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C184" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D184" s="7" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="E184" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F184" s="8">
-        <v>130924.77</v>
+        <v>751498.23999999999</v>
       </c>
       <c r="G184" s="8">
-        <v>81938.42</v>
+        <v>445341.89</v>
       </c>
       <c r="H184" s="7">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="I184" s="7" t="s">
         <v>171</v>
@@ -5536,25 +5564,25 @@
     </row>
     <row r="185" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B185" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D185" s="7" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F185" s="8">
-        <v>751498.23999999999</v>
+        <v>1445822.08</v>
       </c>
       <c r="G185" s="8">
-        <v>445341.89</v>
+        <v>838393.34</v>
       </c>
       <c r="H185" s="7">
-        <v>0.59</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I185" s="7" t="s">
         <v>171</v>
@@ -5562,25 +5590,25 @@
     </row>
     <row r="186" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B186" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C186" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D186" s="7" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="E186" s="7" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F186" s="8">
-        <v>1445822.08</v>
+        <v>344031.17</v>
       </c>
       <c r="G186" s="8">
-        <v>838393.34</v>
+        <v>197415.36</v>
       </c>
       <c r="H186" s="7">
-        <v>0.57999999999999996</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I186" s="7" t="s">
         <v>171</v>
@@ -5588,25 +5616,25 @@
     </row>
     <row r="187" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B187" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D187" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E187" s="7" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F187" s="8">
-        <v>344031.17</v>
+        <v>512759.98</v>
       </c>
       <c r="G187" s="8">
-        <v>197415.36</v>
+        <v>288754.25</v>
       </c>
       <c r="H187" s="7">
-        <v>0.56999999999999995</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I187" s="7" t="s">
         <v>171</v>
@@ -5614,25 +5642,25 @@
     </row>
     <row r="188" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B188" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C188" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D188" s="7" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E188" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F188" s="8">
-        <v>512759.98</v>
+        <v>2765126.84</v>
       </c>
       <c r="G188" s="8">
-        <v>288754.25</v>
+        <v>1522831</v>
       </c>
       <c r="H188" s="7">
-        <v>0.56000000000000005</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="I188" s="7" t="s">
         <v>171</v>
@@ -5640,25 +5668,25 @@
     </row>
     <row r="189" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B189" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C189" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D189" s="7" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E189" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F189" s="8">
-        <v>2765126.84</v>
+        <v>308079.01</v>
       </c>
       <c r="G189" s="8">
-        <v>1522831</v>
+        <v>159102.01999999999</v>
       </c>
       <c r="H189" s="7">
-        <v>0.55000000000000004</v>
+        <v>0.52</v>
       </c>
       <c r="I189" s="7" t="s">
         <v>171</v>
@@ -5666,7 +5694,7 @@
     </row>
     <row r="190" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B190" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C190" s="7" t="s">
         <v>7</v>
@@ -5675,16 +5703,16 @@
         <v>64</v>
       </c>
       <c r="E190" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F190" s="8">
-        <v>308079.01</v>
+        <v>561717.55000000005</v>
       </c>
       <c r="G190" s="8">
-        <v>159102.01999999999</v>
+        <v>288640.65000000002</v>
       </c>
       <c r="H190" s="7">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="I190" s="7" t="s">
         <v>171</v>
@@ -5692,25 +5720,25 @@
     </row>
     <row r="191" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B191" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C191" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D191" s="7" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="E191" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F191" s="8">
-        <v>561717.55000000005</v>
+        <v>410363.31</v>
       </c>
       <c r="G191" s="8">
-        <v>288640.65000000002</v>
+        <v>191113.86</v>
       </c>
       <c r="H191" s="7">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="I191" s="7" t="s">
         <v>171</v>
@@ -5718,25 +5746,25 @@
     </row>
     <row r="192" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B192" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C192" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D192" s="7" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="E192" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F192" s="8">
-        <v>410363.31</v>
+        <v>615076.21</v>
       </c>
       <c r="G192" s="8">
-        <v>191113.86</v>
+        <v>270498.58</v>
       </c>
       <c r="H192" s="7">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="I192" s="7" t="s">
         <v>171</v>
@@ -5744,25 +5772,25 @@
     </row>
     <row r="193" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B193" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C193" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D193" s="7" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="E193" s="7" t="s">
         <v>39</v>
       </c>
       <c r="F193" s="8">
-        <v>615076.21</v>
+        <v>476955.62</v>
       </c>
       <c r="G193" s="8">
-        <v>270498.58</v>
+        <v>205778.71</v>
       </c>
       <c r="H193" s="7">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="I193" s="7" t="s">
         <v>171</v>
@@ -5770,22 +5798,22 @@
     </row>
     <row r="194" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B194" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C194" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D194" s="7" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E194" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F194" s="8">
-        <v>476955.62</v>
+        <v>792511.06</v>
       </c>
       <c r="G194" s="8">
-        <v>205778.71</v>
+        <v>338144.12</v>
       </c>
       <c r="H194" s="7">
         <v>0.43</v>
@@ -5796,25 +5824,25 @@
     </row>
     <row r="195" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B195" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C195" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D195" s="7" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="E195" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F195" s="8">
-        <v>792511.06</v>
+        <v>455293.17</v>
       </c>
       <c r="G195" s="8">
-        <v>338144.12</v>
+        <v>185403.81</v>
       </c>
       <c r="H195" s="7">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="I195" s="7" t="s">
         <v>171</v>
@@ -5822,22 +5850,22 @@
     </row>
     <row r="196" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B196" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C196" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D196" s="7" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="E196" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F196" s="8">
-        <v>455293.17</v>
+        <v>676598.54</v>
       </c>
       <c r="G196" s="8">
-        <v>185403.81</v>
+        <v>277815.11</v>
       </c>
       <c r="H196" s="7">
         <v>0.41</v>
@@ -5848,25 +5876,25 @@
     </row>
     <row r="197" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B197" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D197" s="7" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="E197" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F197" s="8">
-        <v>676598.54</v>
+        <v>1714897.17</v>
       </c>
       <c r="G197" s="8">
-        <v>277815.11</v>
+        <v>672946.89</v>
       </c>
       <c r="H197" s="7">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="I197" s="7" t="s">
         <v>171</v>
@@ -5874,25 +5902,25 @@
     </row>
     <row r="198" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B198" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C198" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D198" s="7" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="E198" s="7" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F198" s="8">
-        <v>1714897.17</v>
+        <v>4200985.63</v>
       </c>
       <c r="G198" s="8">
-        <v>672946.89</v>
+        <v>1582714.69</v>
       </c>
       <c r="H198" s="7">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="I198" s="7" t="s">
         <v>171</v>
@@ -5900,22 +5928,22 @@
     </row>
     <row r="199" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B199" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D199" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E199" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F199" s="8">
-        <v>4200985.63</v>
+        <v>588586.51</v>
       </c>
       <c r="G199" s="8">
-        <v>1582714.69</v>
+        <v>223027.95</v>
       </c>
       <c r="H199" s="7">
         <v>0.38</v>
@@ -5926,25 +5954,25 @@
     </row>
     <row r="200" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B200" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C200" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D200" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E200" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F200" s="8">
-        <v>588586.51</v>
+        <v>694853.8</v>
       </c>
       <c r="G200" s="8">
-        <v>223027.95</v>
+        <v>241379.72</v>
       </c>
       <c r="H200" s="7">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="I200" s="7" t="s">
         <v>171</v>
@@ -5952,25 +5980,25 @@
     </row>
     <row r="201" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B201" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D201" s="7" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="E201" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F201" s="8">
-        <v>694853.8</v>
+        <v>3804625</v>
       </c>
       <c r="G201" s="8">
-        <v>241379.72</v>
+        <v>1285492.58</v>
       </c>
       <c r="H201" s="7">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="I201" s="7" t="s">
         <v>171</v>
@@ -5978,25 +6006,25 @@
     </row>
     <row r="202" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B202" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C202" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D202" s="7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E202" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F202" s="8">
-        <v>3804625</v>
+        <v>1876196.75</v>
       </c>
       <c r="G202" s="8">
-        <v>1285492.58</v>
+        <v>612419.98</v>
       </c>
       <c r="H202" s="7">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="I202" s="7" t="s">
         <v>171</v>
@@ -6004,25 +6032,25 @@
     </row>
     <row r="203" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B203" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D203" s="7" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="E203" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F203" s="8">
-        <v>1876196.75</v>
+        <v>283449.02</v>
       </c>
       <c r="G203" s="8">
-        <v>612419.98</v>
+        <v>88144.79</v>
       </c>
       <c r="H203" s="7">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="I203" s="7" t="s">
         <v>171</v>
@@ -6030,22 +6058,22 @@
     </row>
     <row r="204" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B204" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C204" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D204" s="7" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="E204" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F204" s="8">
-        <v>283449.02</v>
+        <v>744696.92</v>
       </c>
       <c r="G204" s="8">
-        <v>88144.79</v>
+        <v>227298.61</v>
       </c>
       <c r="H204" s="7">
         <v>0.31</v>
@@ -6056,22 +6084,22 @@
     </row>
     <row r="205" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B205" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D205" s="7" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F205" s="8">
-        <v>744696.92</v>
+        <v>1349869.65</v>
       </c>
       <c r="G205" s="8">
-        <v>227298.61</v>
+        <v>423273.76</v>
       </c>
       <c r="H205" s="7">
         <v>0.31</v>
@@ -6082,22 +6110,22 @@
     </row>
     <row r="206" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B206" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C206" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D206" s="7" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="E206" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F206" s="8">
-        <v>1349869.65</v>
+        <v>2164013.04</v>
       </c>
       <c r="G206" s="8">
-        <v>423273.76</v>
+        <v>669510.68000000005</v>
       </c>
       <c r="H206" s="7">
         <v>0.31</v>
@@ -6108,25 +6136,25 @@
     </row>
     <row r="207" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B207" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D207" s="7" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="E207" s="7" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F207" s="8">
-        <v>2164013.04</v>
+        <v>648381.14</v>
       </c>
       <c r="G207" s="8">
-        <v>669510.68000000005</v>
+        <v>191534.04</v>
       </c>
       <c r="H207" s="7">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="I207" s="7" t="s">
         <v>171</v>
@@ -6134,22 +6162,22 @@
     </row>
     <row r="208" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B208" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C208" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D208" s="7" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F208" s="8">
-        <v>648381.14</v>
+        <v>398756.14</v>
       </c>
       <c r="G208" s="8">
-        <v>191534.04</v>
+        <v>120657.3</v>
       </c>
       <c r="H208" s="7">
         <v>0.3</v>
@@ -6160,22 +6188,22 @@
     </row>
     <row r="209" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B209" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C209" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D209" s="7" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="E209" s="7" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F209" s="8">
-        <v>398756.14</v>
+        <v>293200.99</v>
       </c>
       <c r="G209" s="8">
-        <v>120657.3</v>
+        <v>86821.06</v>
       </c>
       <c r="H209" s="7">
         <v>0.3</v>
@@ -6186,22 +6214,22 @@
     </row>
     <row r="210" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B210" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C210" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D210" s="7" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E210" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F210" s="8">
-        <v>293200.99</v>
+        <v>313286.95</v>
       </c>
       <c r="G210" s="8">
-        <v>86821.06</v>
+        <v>94614.7</v>
       </c>
       <c r="H210" s="7">
         <v>0.3</v>
@@ -6212,25 +6240,25 @@
     </row>
     <row r="211" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B211" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C211" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D211" s="7" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="E211" s="7" t="s">
         <v>39</v>
       </c>
       <c r="F211" s="8">
-        <v>313286.95</v>
+        <v>748606.08</v>
       </c>
       <c r="G211" s="8">
-        <v>94614.7</v>
+        <v>214552.06</v>
       </c>
       <c r="H211" s="7">
-        <v>0.3</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I211" s="7" t="s">
         <v>171</v>
@@ -6238,22 +6266,22 @@
     </row>
     <row r="212" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B212" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D212" s="7" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="E212" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F212" s="8">
-        <v>748606.08</v>
+        <v>1373697.15</v>
       </c>
       <c r="G212" s="8">
-        <v>214552.06</v>
+        <v>399821.27</v>
       </c>
       <c r="H212" s="7">
         <v>0.28999999999999998</v>
@@ -6264,22 +6292,22 @@
     </row>
     <row r="213" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B213" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D213" s="7" t="s">
         <v>51</v>
       </c>
       <c r="E213" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F213" s="8">
-        <v>1373697.15</v>
+        <v>759036.85</v>
       </c>
       <c r="G213" s="8">
-        <v>399821.27</v>
+        <v>221024.47</v>
       </c>
       <c r="H213" s="7">
         <v>0.28999999999999998</v>
@@ -6290,25 +6318,25 @@
     </row>
     <row r="214" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B214" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C214" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D214" s="7" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="E214" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F214" s="8">
-        <v>759036.85</v>
+        <v>790268.1</v>
       </c>
       <c r="G214" s="8">
-        <v>221024.47</v>
+        <v>219844.42</v>
       </c>
       <c r="H214" s="7">
-        <v>0.28999999999999998</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I214" s="7" t="s">
         <v>171</v>
@@ -6316,22 +6344,22 @@
     </row>
     <row r="215" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B215" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D215" s="7" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="E215" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F215" s="8">
-        <v>790268.1</v>
+        <v>1843501.32</v>
       </c>
       <c r="G215" s="8">
-        <v>219844.42</v>
+        <v>520218.16</v>
       </c>
       <c r="H215" s="7">
         <v>0.28000000000000003</v>
@@ -6342,25 +6370,25 @@
     </row>
     <row r="216" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B216" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C216" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D216" s="7" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E216" s="7" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F216" s="8">
-        <v>1843501.32</v>
+        <v>4819644.7300000004</v>
       </c>
       <c r="G216" s="8">
-        <v>520218.16</v>
+        <v>1291064.75</v>
       </c>
       <c r="H216" s="7">
-        <v>0.28000000000000003</v>
+        <v>0.27</v>
       </c>
       <c r="I216" s="7" t="s">
         <v>171</v>
@@ -6368,25 +6396,25 @@
     </row>
     <row r="217" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B217" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C217" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D217" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E217" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F217" s="8">
-        <v>4819644.7300000004</v>
+        <v>542798.26</v>
       </c>
       <c r="G217" s="8">
-        <v>1291064.75</v>
+        <v>131769.26</v>
       </c>
       <c r="H217" s="7">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="I217" s="7" t="s">
         <v>171</v>
@@ -6394,7 +6422,7 @@
     </row>
     <row r="218" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B218" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C218" s="7" t="s">
         <v>7</v>
@@ -6403,16 +6431,16 @@
         <v>45</v>
       </c>
       <c r="E218" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F218" s="8">
-        <v>542798.26</v>
+        <v>737972.2</v>
       </c>
       <c r="G218" s="8">
-        <v>131769.26</v>
+        <v>164625.45000000001</v>
       </c>
       <c r="H218" s="7">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="I218" s="7" t="s">
         <v>171</v>
@@ -6420,22 +6448,22 @@
     </row>
     <row r="219" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B219" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C219" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D219" s="7" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="E219" s="7" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F219" s="8">
-        <v>737972.2</v>
+        <v>1397779.99</v>
       </c>
       <c r="G219" s="8">
-        <v>164625.45000000001</v>
+        <v>301552.09999999998</v>
       </c>
       <c r="H219" s="7">
         <v>0.22</v>
@@ -6446,25 +6474,25 @@
     </row>
     <row r="220" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B220" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C220" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D220" s="7" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="E220" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F220" s="8">
-        <v>1397779.99</v>
+        <v>480816.9</v>
       </c>
       <c r="G220" s="8">
-        <v>301552.09999999998</v>
+        <v>100599.41</v>
       </c>
       <c r="H220" s="7">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="I220" s="7" t="s">
         <v>171</v>
@@ -6472,22 +6500,22 @@
     </row>
     <row r="221" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B221" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D221" s="7" t="s">
         <v>29</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F221" s="8">
-        <v>480816.9</v>
+        <v>3032468.39</v>
       </c>
       <c r="G221" s="8">
-        <v>100599.41</v>
+        <v>648096.81999999995</v>
       </c>
       <c r="H221" s="7">
         <v>0.21</v>
@@ -6498,25 +6526,25 @@
     </row>
     <row r="222" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B222" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C222" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D222" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F222" s="8">
-        <v>3032468.39</v>
+        <v>3866669.43</v>
       </c>
       <c r="G222" s="8">
-        <v>648096.81999999995</v>
+        <v>688053.89</v>
       </c>
       <c r="H222" s="7">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="I222" s="7" t="s">
         <v>171</v>
@@ -6524,25 +6552,25 @@
     </row>
     <row r="223" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B223" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C223" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D223" s="7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E223" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F223" s="8">
-        <v>3866669.43</v>
+        <v>4051348.23</v>
       </c>
       <c r="G223" s="8">
-        <v>688053.89</v>
+        <v>696580.05</v>
       </c>
       <c r="H223" s="7">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="I223" s="7" t="s">
         <v>171</v>
@@ -6550,22 +6578,22 @@
     </row>
     <row r="224" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B224" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C224" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D224" s="7" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="E224" s="7" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F224" s="8">
-        <v>4051348.23</v>
+        <v>4784741.2699999996</v>
       </c>
       <c r="G224" s="8">
-        <v>696580.05</v>
+        <v>798213.73</v>
       </c>
       <c r="H224" s="7">
         <v>0.17</v>
@@ -6576,25 +6604,25 @@
     </row>
     <row r="225" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B225" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C225" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D225" s="7" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F225" s="8">
-        <v>4784741.2699999996</v>
+        <v>1025942.44</v>
       </c>
       <c r="G225" s="8">
-        <v>798213.73</v>
+        <v>162254.1</v>
       </c>
       <c r="H225" s="7">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="I225" s="7" t="s">
         <v>171</v>
@@ -6602,22 +6630,22 @@
     </row>
     <row r="226" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B226" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C226" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D226" s="7" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="E226" s="7" t="s">
         <v>39</v>
       </c>
       <c r="F226" s="8">
-        <v>1025942.44</v>
+        <v>1346362.37</v>
       </c>
       <c r="G226" s="8">
-        <v>162254.1</v>
+        <v>220005.03</v>
       </c>
       <c r="H226" s="7">
         <v>0.16</v>
@@ -6628,25 +6656,25 @@
     </row>
     <row r="227" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B227" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C227" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D227" s="7" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="E227" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F227" s="8">
-        <v>1346362.37</v>
+        <v>654003.31000000006</v>
       </c>
       <c r="G227" s="8">
-        <v>220005.03</v>
+        <v>99007.42</v>
       </c>
       <c r="H227" s="7">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I227" s="7" t="s">
         <v>171</v>
@@ -6654,22 +6682,22 @@
     </row>
     <row r="228" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B228" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C228" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D228" s="7" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="E228" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F228" s="8">
-        <v>654003.31000000006</v>
+        <v>548500.28</v>
       </c>
       <c r="G228" s="8">
-        <v>99007.42</v>
+        <v>80418.64</v>
       </c>
       <c r="H228" s="7">
         <v>0.15</v>
@@ -6680,22 +6708,22 @@
     </row>
     <row r="229" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B229" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D229" s="7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E229" s="7" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F229" s="8">
-        <v>548500.28</v>
+        <v>4656365.46</v>
       </c>
       <c r="G229" s="8">
-        <v>80418.64</v>
+        <v>679247.07</v>
       </c>
       <c r="H229" s="7">
         <v>0.15</v>
@@ -6706,25 +6734,25 @@
     </row>
     <row r="230" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B230" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C230" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D230" s="7" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="E230" s="7" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F230" s="8">
-        <v>4656365.46</v>
+        <v>2491412.25</v>
       </c>
       <c r="G230" s="8">
-        <v>679247.07</v>
+        <v>337789.9</v>
       </c>
       <c r="H230" s="7">
-        <v>0.15</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="I230" s="7" t="s">
         <v>171</v>
@@ -6732,22 +6760,22 @@
     </row>
     <row r="231" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B231" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C231" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D231" s="7" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="E231" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F231" s="8">
-        <v>2491412.25</v>
+        <v>1902192.56</v>
       </c>
       <c r="G231" s="8">
-        <v>337789.9</v>
+        <v>270822.90000000002</v>
       </c>
       <c r="H231" s="7">
         <v>0.14000000000000001</v>
@@ -6758,22 +6786,22 @@
     </row>
     <row r="232" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B232" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C232" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D232" s="7" t="s">
         <v>69</v>
       </c>
       <c r="E232" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F232" s="8">
-        <v>1902192.56</v>
+        <v>685601.66</v>
       </c>
       <c r="G232" s="8">
-        <v>270822.90000000002</v>
+        <v>95827.96</v>
       </c>
       <c r="H232" s="7">
         <v>0.14000000000000001</v>
@@ -6784,25 +6812,25 @@
     </row>
     <row r="233" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B233" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C233" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D233" s="7" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="E233" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F233" s="8">
-        <v>685601.66</v>
+        <v>533161.77</v>
       </c>
       <c r="G233" s="8">
-        <v>95827.96</v>
+        <v>70154.92</v>
       </c>
       <c r="H233" s="7">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="I233" s="7" t="s">
         <v>171</v>
@@ -6810,22 +6838,22 @@
     </row>
     <row r="234" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B234" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C234" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D234" s="7" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E234" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F234" s="8">
-        <v>533161.77</v>
+        <v>3937359.95</v>
       </c>
       <c r="G234" s="8">
-        <v>70154.92</v>
+        <v>512660.74</v>
       </c>
       <c r="H234" s="7">
         <v>0.13</v>
@@ -6836,25 +6864,25 @@
     </row>
     <row r="235" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B235" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C235" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D235" s="7" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="E235" s="7" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F235" s="8">
-        <v>3937359.95</v>
+        <v>763175.73</v>
       </c>
       <c r="G235" s="8">
-        <v>512660.74</v>
+        <v>95159.3</v>
       </c>
       <c r="H235" s="7">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I235" s="7" t="s">
         <v>171</v>
@@ -6862,7 +6890,7 @@
     </row>
     <row r="236" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B236" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C236" s="7" t="s">
         <v>7</v>
@@ -6871,13 +6899,13 @@
         <v>84</v>
       </c>
       <c r="E236" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F236" s="8">
-        <v>763175.73</v>
+        <v>371293.4</v>
       </c>
       <c r="G236" s="8">
-        <v>95159.3</v>
+        <v>43971.74</v>
       </c>
       <c r="H236" s="7">
         <v>0.12</v>
@@ -6888,22 +6916,22 @@
     </row>
     <row r="237" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B237" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C237" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D237" s="7" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="E237" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F237" s="8">
-        <v>371293.4</v>
+        <v>4255054.24</v>
       </c>
       <c r="G237" s="8">
-        <v>43971.74</v>
+        <v>504048.4</v>
       </c>
       <c r="H237" s="7">
         <v>0.12</v>
@@ -6914,25 +6942,25 @@
     </row>
     <row r="238" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B238" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C238" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D238" s="7" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E238" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F238" s="8">
-        <v>4255054.24</v>
+        <v>2698415.62</v>
       </c>
       <c r="G238" s="8">
-        <v>504048.4</v>
+        <v>286882.15000000002</v>
       </c>
       <c r="H238" s="7">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="I238" s="7" t="s">
         <v>171</v>
@@ -6940,22 +6968,22 @@
     </row>
     <row r="239" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B239" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C239" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D239" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E239" s="7" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F239" s="8">
-        <v>2698415.62</v>
+        <v>450144.89</v>
       </c>
       <c r="G239" s="8">
-        <v>286882.15000000002</v>
+        <v>48685.17</v>
       </c>
       <c r="H239" s="7">
         <v>0.11</v>
@@ -6966,25 +6994,25 @@
     </row>
     <row r="240" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B240" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C240" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D240" s="7" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="E240" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F240" s="8">
-        <v>450144.89</v>
+        <v>438249.71</v>
       </c>
       <c r="G240" s="8">
-        <v>48685.17</v>
+        <v>37857.19</v>
       </c>
       <c r="H240" s="7">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I240" s="7" t="s">
         <v>171</v>
@@ -6992,25 +7020,25 @@
     </row>
     <row r="241" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B241" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C241" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D241" s="7" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="E241" s="7" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F241" s="8">
-        <v>438249.71</v>
+        <v>3493674.37</v>
       </c>
       <c r="G241" s="8">
-        <v>37857.19</v>
+        <v>268039.19</v>
       </c>
       <c r="H241" s="7">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="I241" s="7" t="s">
         <v>171</v>
@@ -7018,25 +7046,25 @@
     </row>
     <row r="242" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B242" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C242" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D242" s="7" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="E242" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F242" s="8">
-        <v>3493674.37</v>
+        <v>3341233.04</v>
       </c>
       <c r="G242" s="8">
-        <v>268039.19</v>
+        <v>228525.23</v>
       </c>
       <c r="H242" s="7">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I242" s="7" t="s">
         <v>171</v>
@@ -7044,22 +7072,22 @@
     </row>
     <row r="243" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B243" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C243" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D243" s="7" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="E243" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F243" s="8">
-        <v>3341233.04</v>
+        <v>4916005.1399999997</v>
       </c>
       <c r="G243" s="8">
-        <v>228525.23</v>
+        <v>332707.26</v>
       </c>
       <c r="H243" s="7">
         <v>7.0000000000000007E-2</v>
@@ -7070,22 +7098,22 @@
     </row>
     <row r="244" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B244" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C244" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D244" s="7" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="E244" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F244" s="8">
-        <v>4916005.1399999997</v>
+        <v>763802.16</v>
       </c>
       <c r="G244" s="8">
-        <v>332707.26</v>
+        <v>50559.21</v>
       </c>
       <c r="H244" s="7">
         <v>7.0000000000000007E-2</v>
@@ -7096,22 +7124,22 @@
     </row>
     <row r="245" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B245" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C245" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D245" s="7" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="E245" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F245" s="8">
-        <v>763802.16</v>
+        <v>2228393.1800000002</v>
       </c>
       <c r="G245" s="8">
-        <v>50559.21</v>
+        <v>150908.71</v>
       </c>
       <c r="H245" s="7">
         <v>7.0000000000000007E-2</v>
@@ -7122,25 +7150,25 @@
     </row>
     <row r="246" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B246" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C246" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D246" s="7" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="E246" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F246" s="8">
-        <v>2228393.1800000002</v>
+        <v>2527973.5299999998</v>
       </c>
       <c r="G246" s="8">
-        <v>150908.71</v>
+        <v>157162.14000000001</v>
       </c>
       <c r="H246" s="7">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="I246" s="7" t="s">
         <v>171</v>
@@ -7148,25 +7176,25 @@
     </row>
     <row r="247" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B247" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D247" s="7" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="E247" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F247" s="8">
-        <v>2527973.5299999998</v>
+        <v>787703.96</v>
       </c>
       <c r="G247" s="8">
-        <v>157162.14000000001</v>
+        <v>39948.720000000001</v>
       </c>
       <c r="H247" s="7">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="I247" s="7" t="s">
         <v>171</v>
@@ -7174,25 +7202,22 @@
     </row>
     <row r="248" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B248" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C248" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="D248" s="7" t="s">
-        <v>84</v>
       </c>
       <c r="E248" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F248" s="8">
-        <v>787703.96</v>
+        <v>474054</v>
       </c>
       <c r="G248" s="8">
-        <v>39948.720000000001</v>
+        <v>16258.84</v>
       </c>
       <c r="H248" s="7">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="I248" s="7" t="s">
         <v>171</v>
@@ -7200,19 +7225,22 @@
     </row>
     <row r="249" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B249" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C249" s="7" t="s">
         <v>7</v>
       </c>
+      <c r="D249" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="E249" s="7" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F249" s="8">
-        <v>474054</v>
+        <v>715621.65</v>
       </c>
       <c r="G249" s="8">
-        <v>16258.84</v>
+        <v>21623.27</v>
       </c>
       <c r="H249" s="7">
         <v>0.03</v>
@@ -7223,25 +7251,25 @@
     </row>
     <row r="250" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B250" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C250" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D250" s="7" t="s">
         <v>55</v>
       </c>
       <c r="E250" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F250" s="8">
-        <v>715621.65</v>
+        <v>4361511.1399999997</v>
       </c>
       <c r="G250" s="8">
-        <v>21623.27</v>
+        <v>43442.68</v>
       </c>
       <c r="H250" s="7">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="I250" s="7" t="s">
         <v>171</v>
@@ -7249,22 +7277,22 @@
     </row>
     <row r="251" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B251" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C251" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D251" s="7" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="E251" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F251" s="8">
-        <v>4361511.1399999997</v>
+        <v>3540299.3</v>
       </c>
       <c r="G251" s="8">
-        <v>43442.68</v>
+        <v>30876.81</v>
       </c>
       <c r="H251" s="7">
         <v>0.01</v>
@@ -7273,330 +7301,318 @@
         <v>171</v>
       </c>
     </row>
-    <row r="252" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B252" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="C252" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D252" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E252" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F252" s="8">
-        <v>3540299.3</v>
-      </c>
-      <c r="G252" s="8">
-        <v>30876.81</v>
-      </c>
-      <c r="H252" s="7">
-        <v>0.01</v>
-      </c>
-      <c r="I252" s="7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="257" spans="2:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B257" s="5" t="s">
+    <row r="256" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B256" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="C257" s="6"/>
-      <c r="D257" s="6"/>
+      <c r="C256" s="6"/>
+      <c r="D256" s="6"/>
+    </row>
+    <row r="258" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B258" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C258" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D258" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="E258" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="F258" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="G258" s="7" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="259" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B259" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C259" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D259" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="E259" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="F259" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="G259" s="7" t="s">
-        <v>269</v>
+        <v>8</v>
+      </c>
+      <c r="C259" s="7">
+        <v>35</v>
+      </c>
+      <c r="D259" s="7">
+        <v>6</v>
+      </c>
+      <c r="E259" s="7">
+        <v>8</v>
+      </c>
+      <c r="F259" s="7">
+        <v>21</v>
+      </c>
+      <c r="G259" s="7">
+        <v>17.100000000000001</v>
       </c>
     </row>
     <row r="260" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B260" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C260" s="7">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D260" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E260" s="7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F260" s="7">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G260" s="7">
-        <v>17.100000000000001</v>
+        <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="261" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B261" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C261" s="7">
-        <v>41</v>
+        <v>138</v>
       </c>
       <c r="D261" s="7">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E261" s="7">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="F261" s="7">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="G261" s="7">
-        <v>9.8000000000000007</v>
-      </c>
-    </row>
-    <row r="262" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B262" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C262" s="7">
-        <v>138</v>
-      </c>
-      <c r="D262" s="7">
-        <v>12</v>
-      </c>
-      <c r="E262" s="7">
-        <v>43</v>
-      </c>
-      <c r="F262" s="7">
-        <v>83</v>
-      </c>
-      <c r="G262" s="7">
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="266" spans="2:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B266" s="5" t="s">
+    <row r="265" spans="2:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B265" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="C266" s="6"/>
+      <c r="C265" s="6"/>
+    </row>
+    <row r="267" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B267" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="268" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B268" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D268" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="E268" s="2" t="s">
-        <v>269</v>
+        <v>39</v>
+      </c>
+      <c r="C268" s="2">
+        <v>50</v>
+      </c>
+      <c r="D268" s="2">
+        <v>8</v>
+      </c>
+      <c r="E268" s="2">
+        <v>16</v>
       </c>
     </row>
     <row r="269" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B269" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C269" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D269" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E269" s="2">
-        <v>16</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="270" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B270" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C270" s="2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D270" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E270" s="2">
-        <v>11.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="271" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B271" s="2" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="C271" s="2">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D271" s="2">
         <v>4</v>
       </c>
       <c r="E271" s="2">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="272" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B272" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C272" s="2">
-        <v>59</v>
-      </c>
-      <c r="D272" s="2">
-        <v>4</v>
-      </c>
-      <c r="E272" s="2">
         <v>6.8</v>
       </c>
     </row>
-    <row r="275" spans="2:5" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B275" s="5" t="s">
+    <row r="274" spans="2:5" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B274" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="C275" s="6"/>
+      <c r="C274" s="6"/>
+    </row>
+    <row r="276" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B276" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="277" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B277" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C277" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D277" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="E277" s="2" t="s">
-        <v>270</v>
+        <v>38</v>
+      </c>
+      <c r="C277" s="2">
+        <v>24</v>
+      </c>
+      <c r="D277" s="2">
+        <v>4</v>
+      </c>
+      <c r="E277" s="2">
+        <v>16.7</v>
       </c>
     </row>
     <row r="278" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B278" s="2" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="C278" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D278" s="2">
         <v>4</v>
       </c>
       <c r="E278" s="2">
-        <v>16.7</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="279" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B279" s="2" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="C279" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D279" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E279" s="2">
-        <v>14.8</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="280" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B280" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C280" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D280" s="2">
         <v>3</v>
       </c>
       <c r="E280" s="2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="281" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B281" s="2" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="C281" s="2">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D281" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E281" s="2">
-        <v>12</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="282" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B282" s="2" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C282" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D282" s="2">
         <v>2</v>
       </c>
       <c r="E282" s="2">
-        <v>11.8</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="283" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B283" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C283" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D283" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E283" s="2">
-        <v>10.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="284" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B284" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C284" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D284" s="2">
         <v>1</v>
       </c>
       <c r="E284" s="2">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="285" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B285" s="2" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="C285" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D285" s="2">
         <v>1</v>
       </c>
       <c r="E285" s="2">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="286" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B286" s="2" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="C286" s="2">
         <v>22</v>
@@ -7608,63 +7624,69 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="287" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B287" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C287" s="2">
-        <v>22</v>
-      </c>
-      <c r="D287" s="2">
-        <v>1</v>
-      </c>
-      <c r="E287" s="2">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="291" spans="2:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B291" s="5" t="s">
+    <row r="290" spans="2:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B290" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="C291" s="6"/>
-      <c r="D291" s="6"/>
-      <c r="E291" s="6"/>
+      <c r="C290" s="6"/>
+      <c r="D290" s="6"/>
+      <c r="E290" s="6"/>
+    </row>
+    <row r="292" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B292" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E292" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F292" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G292" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="293" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B293" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D293" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E293" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F293" s="2" t="s">
-        <v>270</v>
+        <v>39</v>
+      </c>
+      <c r="D293" s="2">
+        <v>13</v>
+      </c>
+      <c r="E293" s="2">
+        <v>4</v>
+      </c>
+      <c r="F293" s="2">
+        <v>30.8</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>27</v>
+        <v>266</v>
       </c>
     </row>
     <row r="294" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B294" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D294" s="2">
         <v>13</v>
       </c>
       <c r="E294" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F294" s="2">
-        <v>30.8</v>
+        <v>15.4</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>266</v>
@@ -7675,16 +7697,16 @@
         <v>6</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D295" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E295" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F295" s="2">
-        <v>15.4</v>
+        <v>14.3</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>266</v>
@@ -7692,19 +7714,19 @@
     </row>
     <row r="296" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B296" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D296" s="2">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E296" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F296" s="2">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>266</v>
@@ -7712,19 +7734,19 @@
     </row>
     <row r="297" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B297" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D297" s="2">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E297" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F297" s="2">
-        <v>13.3</v>
+        <v>12.5</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>266</v>
@@ -7735,16 +7757,16 @@
         <v>8</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D298" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E298" s="2">
         <v>1</v>
       </c>
       <c r="F298" s="2">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>266</v>
@@ -7752,22 +7774,22 @@
     </row>
     <row r="299" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B299" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C299" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D299" s="2">
         <v>30</v>
       </c>
-      <c r="D299" s="2">
-        <v>9</v>
-      </c>
       <c r="E299" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F299" s="2">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="300" spans="2:7" x14ac:dyDescent="0.25">
@@ -7775,16 +7797,16 @@
         <v>7</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D300" s="2">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E300" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F300" s="2">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>267</v>
@@ -7792,19 +7814,19 @@
     </row>
     <row r="301" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B301" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D301" s="2">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E301" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F301" s="2">
-        <v>9.5</v>
+        <v>7.7</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>267</v>
@@ -7812,19 +7834,19 @@
     </row>
     <row r="302" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B302" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D302" s="2">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E302" s="2">
         <v>1</v>
       </c>
       <c r="F302" s="2">
-        <v>7.7</v>
+        <v>2.8</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>267</v>
@@ -7832,19 +7854,19 @@
     </row>
     <row r="303" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B303" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D303" s="2">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E303" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F303" s="2">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>267</v>
@@ -7852,13 +7874,13 @@
     </row>
     <row r="304" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B304" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D304" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E304" s="2">
         <v>0</v>
@@ -7867,26 +7889,6 @@
         <v>0</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="305" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B305" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C305" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D305" s="2">
-        <v>5</v>
-      </c>
-      <c r="E305" s="2">
-        <v>0</v>
-      </c>
-      <c r="F305" s="2">
-        <v>0</v>
-      </c>
-      <c r="G305" s="2" t="s">
         <v>267</v>
       </c>
     </row>
